--- a/résultat_Tabou_v2.xlsx
+++ b/résultat_Tabou_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robau\OneDrive\Bureau\Polytech\4A\Optimisation discrète\Projet\knapsack_problem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA13EFCD-196B-4ADE-963B-BFA5BB00D2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F554D84-00B7-450B-B2BB-01C0195CD10C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{FA556888-71C7-44BA-BCFC-48CD02DC929A}"/>
   </bookViews>
@@ -29,11 +29,11 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="20" r:id="rId7"/>
-    <pivotCache cacheId="26" r:id="rId8"/>
-    <pivotCache cacheId="33" r:id="rId9"/>
-    <pivotCache cacheId="39" r:id="rId10"/>
-    <pivotCache cacheId="45" r:id="rId11"/>
+    <pivotCache cacheId="0" r:id="rId7"/>
+    <pivotCache cacheId="1" r:id="rId8"/>
+    <pivotCache cacheId="2" r:id="rId9"/>
+    <pivotCache cacheId="3" r:id="rId10"/>
+    <pivotCache cacheId="4" r:id="rId11"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1631,9 +1631,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1803,20 +1802,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="diamond"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3460,16 +3446,13 @@
               <a:buFontTx/>
               <a:buNone/>
               <a:tabLst/>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+              <a:defRPr>
                 <a:solidFill>
                   <a:sysClr val="windowText" lastClr="000000">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:sysClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US" sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
@@ -3555,20 +3538,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="diamond"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -4634,16 +4604,13 @@
               <a:buFontTx/>
               <a:buNone/>
               <a:tabLst/>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+              <a:defRPr>
                 <a:solidFill>
                   <a:sysClr val="windowText" lastClr="000000">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:sysClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -4707,20 +4674,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="diamond"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -5785,16 +5739,13 @@
               <a:buFontTx/>
               <a:buNone/>
               <a:tabLst/>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+              <a:defRPr>
                 <a:solidFill>
                   <a:sysClr val="windowText" lastClr="000000">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:sysClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -5858,20 +5809,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="diamond"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -6965,20 +6903,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="diamond"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -16203,7 +16128,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{14EAD388-CB39-498E-AAF8-C23FDEEDF022}" name="Tableau croisé dynamique4" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{14EAD388-CB39-498E-AAF8-C23FDEEDF022}" name="Tableau croisé dynamique4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="4">
   <location ref="A77:B83" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -16278,7 +16203,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1AF19EF3-FDFF-433D-AED0-6727B5C3E8C2}" name="Tableau croisé dynamique11" cacheId="45" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1AF19EF3-FDFF-433D-AED0-6727B5C3E8C2}" name="Tableau croisé dynamique11" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="5">
   <location ref="A60:B71" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -16373,7 +16298,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6EB34F02-CFD7-4DF8-A12A-63E3294D3546}" name="Tableau croisé dynamique3" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6EB34F02-CFD7-4DF8-A12A-63E3294D3546}" name="Tableau croisé dynamique3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="5">
   <location ref="A60:B71" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -16468,7 +16393,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{18FEECA9-8FCB-4847-8091-44DAF2F65CD2}" name="Tableau croisé dynamique6" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="11">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{18FEECA9-8FCB-4847-8091-44DAF2F65CD2}" name="Tableau croisé dynamique6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="11">
   <location ref="A77:B83" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -16543,7 +16468,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0234DE0E-72C6-455B-8329-44A432F67343}" name="Tableau croisé dynamique5" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0234DE0E-72C6-455B-8329-44A432F67343}" name="Tableau croisé dynamique5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="7">
   <location ref="A60:B71" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -16638,7 +16563,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96F1C74C-98DB-4AB6-AFF0-0F76A1D53DB6}" name="Tableau croisé dynamique8" cacheId="33" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="8">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96F1C74C-98DB-4AB6-AFF0-0F76A1D53DB6}" name="Tableau croisé dynamique8" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="8">
   <location ref="A77:B83" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -16713,7 +16638,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{221F6A12-814D-4D26-B3D4-FFB52D1D4850}" name="Tableau croisé dynamique7" cacheId="33" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{221F6A12-814D-4D26-B3D4-FFB52D1D4850}" name="Tableau croisé dynamique7" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="5">
   <location ref="A60:B71" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -16808,7 +16733,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BCA2BA42-B4F2-4492-9A0D-111DB0E949E0}" name="Tableau croisé dynamique10" cacheId="39" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BCA2BA42-B4F2-4492-9A0D-111DB0E949E0}" name="Tableau croisé dynamique10" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="6">
   <location ref="A77:B83" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -16883,7 +16808,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{883B343E-E961-4DBC-9CC4-93871A1B0269}" name="Tableau croisé dynamique9" cacheId="39" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{883B343E-E961-4DBC-9CC4-93871A1B0269}" name="Tableau croisé dynamique9" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="6">
   <location ref="A60:B71" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -16978,7 +16903,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EA277161-4A35-4358-A48B-40BFF2D9F5EE}" name="Tableau croisé dynamique12" cacheId="45" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EA277161-4A35-4358-A48B-40BFF2D9F5EE}" name="Tableau croisé dynamique12" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="6">
   <location ref="A77:B83" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -17626,7 +17551,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2">
@@ -17644,10 +17569,10 @@
       <c r="F2">
         <v>970</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>10</v>
       </c>
       <c r="I2">
@@ -17656,7 +17581,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3">
@@ -17674,19 +17599,19 @@
       <c r="F3">
         <v>970</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" t="s">
         <v>12</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I2:I33" si="0">IF(ISNUMBER(G3), G3, SUBSTITUTE(G3, ".", ",")*1)</f>
+        <f t="shared" ref="I3:I33" si="0">IF(ISNUMBER(G3), G3, SUBSTITUTE(G3, ".", ",")*1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4">
@@ -17704,10 +17629,10 @@
       <c r="F4">
         <v>970</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" t="s">
         <v>14</v>
       </c>
       <c r="I4">
@@ -17716,7 +17641,7 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5">
@@ -17734,10 +17659,10 @@
       <c r="F5">
         <v>970</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" t="s">
         <v>15</v>
       </c>
       <c r="I5">
@@ -17746,7 +17671,7 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6">
@@ -17764,10 +17689,10 @@
       <c r="F6">
         <v>970</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" t="s">
         <v>17</v>
       </c>
       <c r="I6">
@@ -17776,7 +17701,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7">
@@ -17794,10 +17719,10 @@
       <c r="F7">
         <v>970</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" t="s">
         <v>19</v>
       </c>
       <c r="I7">
@@ -17806,7 +17731,7 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8">
@@ -17824,10 +17749,10 @@
       <c r="F8">
         <v>970</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" t="s">
         <v>20</v>
       </c>
       <c r="I8">
@@ -17836,7 +17761,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9">
@@ -17854,10 +17779,10 @@
       <c r="F9">
         <v>970</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" t="s">
         <v>22</v>
       </c>
       <c r="I9">
@@ -17866,7 +17791,7 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>8</v>
       </c>
       <c r="B10">
@@ -17884,10 +17809,10 @@
       <c r="F10">
         <v>970</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" t="s">
         <v>24</v>
       </c>
       <c r="I10">
@@ -17896,7 +17821,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>8</v>
       </c>
       <c r="B11">
@@ -17914,10 +17839,10 @@
       <c r="F11">
         <v>970</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" t="s">
         <v>26</v>
       </c>
       <c r="I11">
@@ -17926,7 +17851,7 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>8</v>
       </c>
       <c r="B12">
@@ -17944,10 +17869,10 @@
       <c r="F12">
         <v>811</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" t="s">
         <v>27</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" t="s">
         <v>28</v>
       </c>
       <c r="I12">
@@ -17956,7 +17881,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>8</v>
       </c>
       <c r="B13">
@@ -17974,10 +17899,10 @@
       <c r="F13">
         <v>970</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" t="s">
         <v>30</v>
       </c>
       <c r="I13">
@@ -17986,7 +17911,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>8</v>
       </c>
       <c r="B14">
@@ -18004,10 +17929,10 @@
       <c r="F14">
         <v>970</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" t="s">
         <v>31</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" t="s">
         <v>32</v>
       </c>
       <c r="I14">
@@ -18016,7 +17941,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>8</v>
       </c>
       <c r="B15">
@@ -18034,10 +17959,10 @@
       <c r="F15">
         <v>970</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" t="s">
         <v>33</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" t="s">
         <v>34</v>
       </c>
       <c r="I15">
@@ -18046,7 +17971,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>8</v>
       </c>
       <c r="B16">
@@ -18064,10 +17989,10 @@
       <c r="F16">
         <v>970</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" t="s">
         <v>35</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" t="s">
         <v>36</v>
       </c>
       <c r="I16">
@@ -18076,7 +18001,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>8</v>
       </c>
       <c r="B17">
@@ -18094,10 +18019,10 @@
       <c r="F17">
         <v>849</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" t="s">
         <v>37</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="H17" t="s">
         <v>38</v>
       </c>
       <c r="I17">
@@ -18106,7 +18031,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>8</v>
       </c>
       <c r="B18">
@@ -18124,10 +18049,10 @@
       <c r="F18">
         <v>970</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" t="s">
         <v>39</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H18" t="s">
         <v>40</v>
       </c>
       <c r="I18">
@@ -18136,7 +18061,7 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>8</v>
       </c>
       <c r="B19">
@@ -18154,10 +18079,10 @@
       <c r="F19">
         <v>970</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" t="s">
         <v>41</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H19" t="s">
         <v>42</v>
       </c>
       <c r="I19">
@@ -18166,7 +18091,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>8</v>
       </c>
       <c r="B20">
@@ -18184,10 +18109,10 @@
       <c r="F20">
         <v>887</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" t="s">
         <v>43</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H20" t="s">
         <v>44</v>
       </c>
       <c r="I20">
@@ -18196,7 +18121,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>8</v>
       </c>
       <c r="B21">
@@ -18214,10 +18139,10 @@
       <c r="F21">
         <v>970</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" t="s">
         <v>45</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" t="s">
         <v>46</v>
       </c>
       <c r="I21">
@@ -18226,7 +18151,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>8</v>
       </c>
       <c r="B22">
@@ -18244,10 +18169,10 @@
       <c r="F22">
         <v>970</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" t="s">
         <v>47</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" t="s">
         <v>48</v>
       </c>
       <c r="I22">
@@ -18256,7 +18181,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>8</v>
       </c>
       <c r="B23">
@@ -18274,10 +18199,10 @@
       <c r="F23">
         <v>970</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" t="s">
         <v>11</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" t="s">
         <v>49</v>
       </c>
       <c r="I23">
@@ -18286,7 +18211,7 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>8</v>
       </c>
       <c r="B24">
@@ -18304,10 +18229,10 @@
       <c r="F24">
         <v>970</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" t="s">
         <v>50</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" t="s">
         <v>51</v>
       </c>
       <c r="I24">
@@ -18316,7 +18241,7 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>8</v>
       </c>
       <c r="B25">
@@ -18334,10 +18259,10 @@
       <c r="F25">
         <v>970</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" t="s">
         <v>52</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="H25" t="s">
         <v>53</v>
       </c>
       <c r="I25">
@@ -18346,7 +18271,7 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>8</v>
       </c>
       <c r="B26">
@@ -18364,10 +18289,10 @@
       <c r="F26">
         <v>970</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G26" t="s">
         <v>54</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="H26" t="s">
         <v>55</v>
       </c>
       <c r="I26">
@@ -18376,7 +18301,7 @@
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>8</v>
       </c>
       <c r="B27">
@@ -18394,10 +18319,10 @@
       <c r="F27">
         <v>970</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G27" t="s">
         <v>56</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="H27" t="s">
         <v>57</v>
       </c>
       <c r="I27">
@@ -18406,7 +18331,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>8</v>
       </c>
       <c r="B28">
@@ -18424,10 +18349,10 @@
       <c r="F28">
         <v>970</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" t="s">
         <v>58</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" t="s">
         <v>59</v>
       </c>
       <c r="I28">
@@ -18436,7 +18361,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>8</v>
       </c>
       <c r="B29">
@@ -18454,10 +18379,10 @@
       <c r="F29">
         <v>970</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" t="s">
         <v>60</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="H29" t="s">
         <v>61</v>
       </c>
       <c r="I29">
@@ -18466,7 +18391,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>8</v>
       </c>
       <c r="B30">
@@ -18484,10 +18409,10 @@
       <c r="F30">
         <v>970</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" t="s">
         <v>62</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="H30" t="s">
         <v>63</v>
       </c>
       <c r="I30">
@@ -18496,7 +18421,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>8</v>
       </c>
       <c r="B31">
@@ -18514,10 +18439,10 @@
       <c r="F31">
         <v>970</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" t="s">
         <v>64</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="H31" t="s">
         <v>65</v>
       </c>
       <c r="I31">
@@ -18526,7 +18451,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>8</v>
       </c>
       <c r="B32">
@@ -18544,10 +18469,10 @@
       <c r="F32">
         <v>970</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" t="s">
         <v>66</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="H32" t="s">
         <v>67</v>
       </c>
       <c r="I32">
@@ -18556,7 +18481,7 @@
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>8</v>
       </c>
       <c r="B33">
@@ -18574,10 +18499,10 @@
       <c r="F33">
         <v>970</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" t="s">
         <v>68</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="H33" t="s">
         <v>69</v>
       </c>
       <c r="I33">
@@ -18586,7 +18511,7 @@
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>8</v>
       </c>
       <c r="B34">
@@ -18604,10 +18529,10 @@
       <c r="F34">
         <v>970</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G34" t="s">
         <v>70</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="H34" t="s">
         <v>71</v>
       </c>
       <c r="I34">
@@ -18616,7 +18541,7 @@
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>8</v>
       </c>
       <c r="B35">
@@ -18634,10 +18559,10 @@
       <c r="F35">
         <v>970</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" t="s">
         <v>72</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="H35" t="s">
         <v>73</v>
       </c>
       <c r="I35">
@@ -18646,7 +18571,7 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>8</v>
       </c>
       <c r="B36">
@@ -18664,10 +18589,10 @@
       <c r="F36">
         <v>970</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G36" t="s">
         <v>74</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="H36" t="s">
         <v>75</v>
       </c>
       <c r="I36">
@@ -18676,7 +18601,7 @@
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>8</v>
       </c>
       <c r="B37">
@@ -18694,10 +18619,10 @@
       <c r="F37">
         <v>773</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G37" t="s">
         <v>76</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="H37" t="s">
         <v>77</v>
       </c>
       <c r="I37">
@@ -18706,7 +18631,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>8</v>
       </c>
       <c r="B38">
@@ -18724,10 +18649,10 @@
       <c r="F38">
         <v>970</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="G38" t="s">
         <v>11</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="H38" t="s">
         <v>78</v>
       </c>
       <c r="I38">
@@ -18736,7 +18661,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>8</v>
       </c>
       <c r="B39">
@@ -18754,10 +18679,10 @@
       <c r="F39">
         <v>970</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" t="s">
         <v>79</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="H39" t="s">
         <v>80</v>
       </c>
       <c r="I39">
@@ -18766,7 +18691,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>8</v>
       </c>
       <c r="B40">
@@ -18784,10 +18709,10 @@
       <c r="F40">
         <v>970</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G40" t="s">
         <v>81</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H40" t="s">
         <v>82</v>
       </c>
       <c r="I40">
@@ -18796,7 +18721,7 @@
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>8</v>
       </c>
       <c r="B41">
@@ -18814,10 +18739,10 @@
       <c r="F41">
         <v>970</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G41" t="s">
         <v>83</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H41" t="s">
         <v>84</v>
       </c>
       <c r="I41">
@@ -18826,7 +18751,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>8</v>
       </c>
       <c r="B42">
@@ -18844,10 +18769,10 @@
       <c r="F42">
         <v>773</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G42" t="s">
         <v>85</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="H42" t="s">
         <v>86</v>
       </c>
       <c r="I42">
@@ -18856,7 +18781,7 @@
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>8</v>
       </c>
       <c r="B43">
@@ -18874,10 +18799,10 @@
       <c r="F43">
         <v>970</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G43" t="s">
         <v>87</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="H43" t="s">
         <v>88</v>
       </c>
       <c r="I43">
@@ -18886,7 +18811,7 @@
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>8</v>
       </c>
       <c r="B44">
@@ -18904,10 +18829,10 @@
       <c r="F44">
         <v>970</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="G44" t="s">
         <v>89</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="H44" t="s">
         <v>90</v>
       </c>
       <c r="I44">
@@ -18916,7 +18841,7 @@
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>8</v>
       </c>
       <c r="B45">
@@ -18934,10 +18859,10 @@
       <c r="F45">
         <v>970</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="G45" t="s">
         <v>91</v>
       </c>
-      <c r="H45" s="1" t="s">
+      <c r="H45" t="s">
         <v>92</v>
       </c>
       <c r="I45">
@@ -18946,7 +18871,7 @@
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>8</v>
       </c>
       <c r="B46">
@@ -18964,10 +18889,10 @@
       <c r="F46">
         <v>970</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="G46" t="s">
         <v>11</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="H46" t="s">
         <v>93</v>
       </c>
       <c r="I46">
@@ -18976,7 +18901,7 @@
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>8</v>
       </c>
       <c r="B47">
@@ -18994,10 +18919,10 @@
       <c r="F47">
         <v>811</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="G47" t="s">
         <v>94</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="H47" t="s">
         <v>95</v>
       </c>
       <c r="I47">
@@ -19006,7 +18931,7 @@
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>8</v>
       </c>
       <c r="B48">
@@ -19024,10 +18949,10 @@
       <c r="F48">
         <v>970</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="G48" t="s">
         <v>11</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="H48" t="s">
         <v>96</v>
       </c>
       <c r="I48">
@@ -19036,7 +18961,7 @@
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>8</v>
       </c>
       <c r="B49">
@@ -19054,10 +18979,10 @@
       <c r="F49">
         <v>970</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="G49" t="s">
         <v>97</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="H49" t="s">
         <v>98</v>
       </c>
       <c r="I49">
@@ -19066,7 +18991,7 @@
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>8</v>
       </c>
       <c r="B50">
@@ -19084,10 +19009,10 @@
       <c r="F50">
         <v>970</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="G50" t="s">
         <v>11</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="H50" t="s">
         <v>99</v>
       </c>
       <c r="I50">
@@ -19096,7 +19021,7 @@
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>8</v>
       </c>
       <c r="B51">
@@ -19114,10 +19039,10 @@
       <c r="F51">
         <v>970</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="G51" t="s">
         <v>100</v>
       </c>
-      <c r="H51" s="1" t="s">
+      <c r="H51" t="s">
         <v>101</v>
       </c>
       <c r="I51">
@@ -19144,7 +19069,7 @@
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="1" t="s">
         <v>105</v>
       </c>
       <c r="B60" t="s">
@@ -19152,95 +19077,95 @@
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="3">
+      <c r="A61" s="2">
         <v>50</v>
       </c>
-      <c r="B61" s="1">
+      <c r="B61">
         <v>938.2</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="3">
+      <c r="A62" s="2">
         <v>100</v>
       </c>
-      <c r="B62" s="1">
+      <c r="B62">
         <v>970</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63" s="3">
+      <c r="A63" s="2">
         <v>500</v>
       </c>
-      <c r="B63" s="1">
+      <c r="B63">
         <v>930.6</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64" s="3">
+      <c r="A64" s="2">
         <v>1000</v>
       </c>
-      <c r="B64" s="1">
+      <c r="B64">
         <v>929.2</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="3">
+      <c r="A65" s="2">
         <v>5000</v>
       </c>
-      <c r="B65" s="1">
+      <c r="B65">
         <v>930.6</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="3">
+      <c r="A66" s="2">
         <v>10000</v>
       </c>
-      <c r="B66" s="1">
+      <c r="B66">
         <v>938.2</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="3">
+      <c r="A67" s="2">
         <v>50000</v>
       </c>
-      <c r="B67" s="1">
+      <c r="B67">
         <v>970</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="3">
+      <c r="A68" s="2">
         <v>100000</v>
       </c>
-      <c r="B68" s="1">
+      <c r="B68">
         <v>970</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="3">
+      <c r="A69" s="2">
         <v>500000</v>
       </c>
-      <c r="B69" s="1">
+      <c r="B69">
         <v>970</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="3">
+      <c r="A70" s="2">
         <v>1000000</v>
       </c>
-      <c r="B70" s="1">
+      <c r="B70">
         <v>970</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="3" t="s">
+      <c r="A71" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B71" s="1">
+      <c r="B71">
         <v>951.68</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
+      <c r="A77" s="1" t="s">
         <v>105</v>
       </c>
       <c r="B77" t="s">
@@ -19248,50 +19173,50 @@
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="3">
+      <c r="A78" s="2">
         <v>1</v>
       </c>
-      <c r="B78" s="1">
+      <c r="B78">
         <v>886.7</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="3">
+      <c r="A79" s="2">
         <v>5</v>
       </c>
-      <c r="B79" s="1">
+      <c r="B79">
         <v>970</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="3">
+      <c r="A80" s="2">
         <v>10</v>
       </c>
-      <c r="B80" s="1">
+      <c r="B80">
         <v>970</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81" s="3">
+      <c r="A81" s="2">
         <v>15</v>
       </c>
-      <c r="B81" s="1">
+      <c r="B81">
         <v>970</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82" s="3">
+      <c r="A82" s="2">
         <v>20</v>
       </c>
-      <c r="B82" s="1">
+      <c r="B82">
         <v>961.7</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83" s="3" t="s">
+      <c r="A83" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B83" s="1">
+      <c r="B83">
         <v>951.68</v>
       </c>
     </row>
@@ -19349,7 +19274,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>109</v>
       </c>
       <c r="B2">
@@ -19367,10 +19292,10 @@
       <c r="F2">
         <v>4431</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>110</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>111</v>
       </c>
       <c r="I2">
@@ -19379,7 +19304,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>109</v>
       </c>
       <c r="B3">
@@ -19397,19 +19322,19 @@
       <c r="F3">
         <v>4514</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>112</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" t="s">
         <v>113</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I2:I33" si="0">IF(ISNUMBER(G3), G3, SUBSTITUTE(G3, ".", ",")*1)</f>
+        <f t="shared" ref="I3:I33" si="0">IF(ISNUMBER(G3), G3, SUBSTITUTE(G3, ".", ",")*1)</f>
         <v>251.131772756576</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>109</v>
       </c>
       <c r="B4">
@@ -19427,10 +19352,10 @@
       <c r="F4">
         <v>4476</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>114</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" t="s">
         <v>115</v>
       </c>
       <c r="I4">
@@ -19439,7 +19364,7 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>109</v>
       </c>
       <c r="B5">
@@ -19457,10 +19382,10 @@
       <c r="F5">
         <v>4127</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" t="s">
         <v>116</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" t="s">
         <v>117</v>
       </c>
       <c r="I5">
@@ -19469,7 +19394,7 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>109</v>
       </c>
       <c r="B6">
@@ -19487,10 +19412,10 @@
       <c r="F6">
         <v>4400</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" t="s">
         <v>118</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" t="s">
         <v>119</v>
       </c>
       <c r="I6">
@@ -19499,7 +19424,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>109</v>
       </c>
       <c r="B7">
@@ -19517,10 +19442,10 @@
       <c r="F7">
         <v>4241</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" t="s">
         <v>120</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" t="s">
         <v>121</v>
       </c>
       <c r="I7">
@@ -19529,7 +19454,7 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>109</v>
       </c>
       <c r="B8">
@@ -19547,10 +19472,10 @@
       <c r="F8">
         <v>4362</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" t="s">
         <v>122</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" t="s">
         <v>123</v>
       </c>
       <c r="I8">
@@ -19559,7 +19484,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>109</v>
       </c>
       <c r="B9">
@@ -19577,10 +19502,10 @@
       <c r="F9">
         <v>4279</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" t="s">
         <v>124</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" t="s">
         <v>125</v>
       </c>
       <c r="I9">
@@ -19589,7 +19514,7 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>109</v>
       </c>
       <c r="B10">
@@ -19607,10 +19532,10 @@
       <c r="F10">
         <v>3975</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" t="s">
         <v>126</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" t="s">
         <v>127</v>
       </c>
       <c r="I10">
@@ -19619,7 +19544,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>109</v>
       </c>
       <c r="B11">
@@ -19637,10 +19562,10 @@
       <c r="F11">
         <v>4476</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" t="s">
         <v>128</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" t="s">
         <v>129</v>
       </c>
       <c r="I11">
@@ -19649,7 +19574,7 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>109</v>
       </c>
       <c r="B12">
@@ -19667,10 +19592,10 @@
       <c r="F12">
         <v>4514</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" t="s">
         <v>130</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" t="s">
         <v>131</v>
       </c>
       <c r="I12">
@@ -19679,7 +19604,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>109</v>
       </c>
       <c r="B13">
@@ -19697,10 +19622,10 @@
       <c r="F13">
         <v>4286</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" t="s">
         <v>132</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" t="s">
         <v>133</v>
       </c>
       <c r="I13">
@@ -19709,7 +19634,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>109</v>
       </c>
       <c r="B14">
@@ -19727,10 +19652,10 @@
       <c r="F14">
         <v>4469</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" t="s">
         <v>134</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" t="s">
         <v>135</v>
       </c>
       <c r="I14">
@@ -19739,7 +19664,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>109</v>
       </c>
       <c r="B15">
@@ -19757,10 +19682,10 @@
       <c r="F15">
         <v>4013</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" t="s">
         <v>136</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" t="s">
         <v>137</v>
       </c>
       <c r="I15">
@@ -19769,7 +19694,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>109</v>
       </c>
       <c r="B16">
@@ -19787,10 +19712,10 @@
       <c r="F16">
         <v>4089</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" t="s">
         <v>138</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" t="s">
         <v>139</v>
       </c>
       <c r="I16">
@@ -19799,7 +19724,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>109</v>
       </c>
       <c r="B17">
@@ -19817,10 +19742,10 @@
       <c r="F17">
         <v>4476</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" t="s">
         <v>140</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="H17" t="s">
         <v>141</v>
       </c>
       <c r="I17">
@@ -19829,7 +19754,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>109</v>
       </c>
       <c r="B18">
@@ -19847,10 +19772,10 @@
       <c r="F18">
         <v>4514</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" t="s">
         <v>142</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H18" t="s">
         <v>143</v>
       </c>
       <c r="I18">
@@ -19859,7 +19784,7 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>109</v>
       </c>
       <c r="B19">
@@ -19877,10 +19802,10 @@
       <c r="F19">
         <v>4514</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" t="s">
         <v>144</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H19" t="s">
         <v>145</v>
       </c>
       <c r="I19">
@@ -19889,7 +19814,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>109</v>
       </c>
       <c r="B20">
@@ -19907,10 +19832,10 @@
       <c r="F20">
         <v>4514</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" t="s">
         <v>146</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H20" t="s">
         <v>147</v>
       </c>
       <c r="I20">
@@ -19919,7 +19844,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>109</v>
       </c>
       <c r="B21">
@@ -19937,10 +19862,10 @@
       <c r="F21">
         <v>4514</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" t="s">
         <v>148</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" t="s">
         <v>149</v>
       </c>
       <c r="I21">
@@ -19949,7 +19874,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -19967,10 +19892,10 @@
       <c r="F22">
         <v>4400</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" t="s">
         <v>150</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" t="s">
         <v>151</v>
       </c>
       <c r="I22">
@@ -19979,7 +19904,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>109</v>
       </c>
       <c r="B23">
@@ -19997,10 +19922,10 @@
       <c r="F23">
         <v>4514</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" t="s">
         <v>152</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" t="s">
         <v>153</v>
       </c>
       <c r="I23">
@@ -20009,7 +19934,7 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>109</v>
       </c>
       <c r="B24">
@@ -20027,10 +19952,10 @@
       <c r="F24">
         <v>4400</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" t="s">
         <v>154</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" t="s">
         <v>155</v>
       </c>
       <c r="I24">
@@ -20039,7 +19964,7 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>109</v>
       </c>
       <c r="B25">
@@ -20057,10 +19982,10 @@
       <c r="F25">
         <v>4514</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" t="s">
         <v>156</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="H25" t="s">
         <v>157</v>
       </c>
       <c r="I25">
@@ -20069,7 +19994,7 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>109</v>
       </c>
       <c r="B26">
@@ -20087,10 +20012,10 @@
       <c r="F26">
         <v>4476</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G26" t="s">
         <v>158</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="H26" t="s">
         <v>159</v>
       </c>
       <c r="I26">
@@ -20099,7 +20024,7 @@
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>109</v>
       </c>
       <c r="B27">
@@ -20117,10 +20042,10 @@
       <c r="F27">
         <v>4082</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G27" t="s">
         <v>160</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="H27" t="s">
         <v>161</v>
       </c>
       <c r="I27">
@@ -20129,7 +20054,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>109</v>
       </c>
       <c r="B28">
@@ -20147,10 +20072,10 @@
       <c r="F28">
         <v>4127</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" t="s">
         <v>162</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" t="s">
         <v>163</v>
       </c>
       <c r="I28">
@@ -20159,7 +20084,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>109</v>
       </c>
       <c r="B29">
@@ -20177,10 +20102,10 @@
       <c r="F29">
         <v>4476</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" t="s">
         <v>164</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="H29" t="s">
         <v>165</v>
       </c>
       <c r="I29">
@@ -20189,7 +20114,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>109</v>
       </c>
       <c r="B30">
@@ -20207,10 +20132,10 @@
       <c r="F30">
         <v>4514</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" t="s">
         <v>166</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="H30" t="s">
         <v>167</v>
       </c>
       <c r="I30">
@@ -20219,7 +20144,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>109</v>
       </c>
       <c r="B31">
@@ -20237,10 +20162,10 @@
       <c r="F31">
         <v>4127</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" t="s">
         <v>168</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="H31" t="s">
         <v>169</v>
       </c>
       <c r="I31">
@@ -20249,7 +20174,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>109</v>
       </c>
       <c r="B32">
@@ -20267,10 +20192,10 @@
       <c r="F32">
         <v>4248</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" t="s">
         <v>170</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="H32" t="s">
         <v>171</v>
       </c>
       <c r="I32">
@@ -20279,7 +20204,7 @@
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>109</v>
       </c>
       <c r="B33">
@@ -20297,10 +20222,10 @@
       <c r="F33">
         <v>4469</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" t="s">
         <v>172</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="H33" t="s">
         <v>173</v>
       </c>
       <c r="I33">
@@ -20309,7 +20234,7 @@
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>109</v>
       </c>
       <c r="B34">
@@ -20327,10 +20252,10 @@
       <c r="F34">
         <v>4051</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G34" t="s">
         <v>174</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="H34" t="s">
         <v>175</v>
       </c>
       <c r="I34">
@@ -20339,7 +20264,7 @@
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>109</v>
       </c>
       <c r="B35">
@@ -20357,10 +20282,10 @@
       <c r="F35">
         <v>4127</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" t="s">
         <v>176</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="H35" t="s">
         <v>177</v>
       </c>
       <c r="I35">
@@ -20369,7 +20294,7 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>109</v>
       </c>
       <c r="B36">
@@ -20387,10 +20312,10 @@
       <c r="F36">
         <v>4476</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G36" t="s">
         <v>178</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="H36" t="s">
         <v>179</v>
       </c>
       <c r="I36">
@@ -20399,7 +20324,7 @@
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>109</v>
       </c>
       <c r="B37">
@@ -20417,10 +20342,10 @@
       <c r="F37">
         <v>4400</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G37" t="s">
         <v>180</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="H37" t="s">
         <v>181</v>
       </c>
       <c r="I37">
@@ -20429,7 +20354,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>109</v>
       </c>
       <c r="B38">
@@ -20447,10 +20372,10 @@
       <c r="F38">
         <v>4514</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="G38" t="s">
         <v>182</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="H38" t="s">
         <v>183</v>
       </c>
       <c r="I38">
@@ -20459,7 +20384,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>109</v>
       </c>
       <c r="B39">
@@ -20477,10 +20402,10 @@
       <c r="F39">
         <v>4514</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" t="s">
         <v>184</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="H39" t="s">
         <v>185</v>
       </c>
       <c r="I39">
@@ -20489,7 +20414,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>109</v>
       </c>
       <c r="B40">
@@ -20507,10 +20432,10 @@
       <c r="F40">
         <v>4514</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G40" t="s">
         <v>186</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H40" t="s">
         <v>187</v>
       </c>
       <c r="I40">
@@ -20519,7 +20444,7 @@
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>109</v>
       </c>
       <c r="B41">
@@ -20537,10 +20462,10 @@
       <c r="F41">
         <v>4469</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G41" t="s">
         <v>188</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H41" t="s">
         <v>189</v>
       </c>
       <c r="I41">
@@ -20549,7 +20474,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>109</v>
       </c>
       <c r="B42">
@@ -20567,10 +20492,10 @@
       <c r="F42">
         <v>4476</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G42" t="s">
         <v>190</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="H42" t="s">
         <v>191</v>
       </c>
       <c r="I42">
@@ -20579,7 +20504,7 @@
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>109</v>
       </c>
       <c r="B43">
@@ -20597,10 +20522,10 @@
       <c r="F43">
         <v>4362</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G43" t="s">
         <v>192</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="H43" t="s">
         <v>193</v>
       </c>
       <c r="I43">
@@ -20609,7 +20534,7 @@
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>109</v>
       </c>
       <c r="B44">
@@ -20627,10 +20552,10 @@
       <c r="F44">
         <v>4476</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="G44" t="s">
         <v>194</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="H44" t="s">
         <v>195</v>
       </c>
       <c r="I44">
@@ -20639,7 +20564,7 @@
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>109</v>
       </c>
       <c r="B45">
@@ -20657,10 +20582,10 @@
       <c r="F45">
         <v>4514</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="G45" t="s">
         <v>196</v>
       </c>
-      <c r="H45" s="1" t="s">
+      <c r="H45" t="s">
         <v>197</v>
       </c>
       <c r="I45">
@@ -20669,7 +20594,7 @@
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>109</v>
       </c>
       <c r="B46">
@@ -20687,10 +20612,10 @@
       <c r="F46">
         <v>4514</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="G46" t="s">
         <v>198</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="H46" t="s">
         <v>199</v>
       </c>
       <c r="I46">
@@ -20699,7 +20624,7 @@
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>109</v>
       </c>
       <c r="B47">
@@ -20717,10 +20642,10 @@
       <c r="F47">
         <v>4476</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="G47" t="s">
         <v>200</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="H47" t="s">
         <v>201</v>
       </c>
       <c r="I47">
@@ -20729,7 +20654,7 @@
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>109</v>
       </c>
       <c r="B48">
@@ -20747,10 +20672,10 @@
       <c r="F48">
         <v>4514</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="G48" t="s">
         <v>202</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="H48" t="s">
         <v>203</v>
       </c>
       <c r="I48">
@@ -20759,7 +20684,7 @@
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>109</v>
       </c>
       <c r="B49">
@@ -20777,10 +20702,10 @@
       <c r="F49">
         <v>4514</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="G49" t="s">
         <v>204</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="H49" t="s">
         <v>205</v>
       </c>
       <c r="I49">
@@ -20789,7 +20714,7 @@
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>109</v>
       </c>
       <c r="B50">
@@ -20807,10 +20732,10 @@
       <c r="F50">
         <v>4514</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="G50" t="s">
         <v>206</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="H50" t="s">
         <v>207</v>
       </c>
       <c r="I50">
@@ -20819,7 +20744,7 @@
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>109</v>
       </c>
       <c r="B51">
@@ -20837,10 +20762,10 @@
       <c r="F51">
         <v>4476</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="G51" t="s">
         <v>208</v>
       </c>
-      <c r="H51" s="1" t="s">
+      <c r="H51" t="s">
         <v>209</v>
       </c>
       <c r="I51">
@@ -20867,7 +20792,7 @@
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="1" t="s">
         <v>105</v>
       </c>
       <c r="B60" t="s">
@@ -20875,95 +20800,95 @@
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="3">
+      <c r="A61" s="2">
         <v>50</v>
       </c>
-      <c r="B61" s="1">
+      <c r="B61">
         <v>4498.8</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="3">
+      <c r="A62" s="2">
         <v>100</v>
       </c>
-      <c r="B62" s="1">
+      <c r="B62">
         <v>4460.8</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63" s="3">
+      <c r="A63" s="2">
         <v>500</v>
       </c>
-      <c r="B63" s="1">
+      <c r="B63">
         <v>4468.3999999999996</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64" s="3">
+      <c r="A64" s="2">
         <v>1000</v>
       </c>
-      <c r="B64" s="1">
+      <c r="B64">
         <v>4506.3999999999996</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="3">
+      <c r="A65" s="2">
         <v>5000</v>
       </c>
-      <c r="B65" s="1">
+      <c r="B65">
         <v>4482.2</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="3">
+      <c r="A66" s="2">
         <v>10000</v>
       </c>
-      <c r="B66" s="1">
+      <c r="B66">
         <v>4274.2</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="3">
+      <c r="A67" s="2">
         <v>50000</v>
       </c>
-      <c r="B67" s="1">
+      <c r="B67">
         <v>4274.2</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="3">
+      <c r="A68" s="2">
         <v>100000</v>
       </c>
-      <c r="B68" s="1">
+      <c r="B68">
         <v>4266.6000000000004</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="3">
+      <c r="A69" s="2">
         <v>500000</v>
       </c>
-      <c r="B69" s="1">
+      <c r="B69">
         <v>4265.2</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="3">
+      <c r="A70" s="2">
         <v>1000000</v>
       </c>
-      <c r="B70" s="1">
+      <c r="B70">
         <v>4389.6000000000004</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="3" t="s">
+      <c r="A71" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B71" s="1">
+      <c r="B71">
         <v>4388.6400000000003</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
+      <c r="A77" s="1" t="s">
         <v>105</v>
       </c>
       <c r="B77" t="s">
@@ -20971,50 +20896,50 @@
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="3">
+      <c r="A78" s="2">
         <v>1</v>
       </c>
-      <c r="B78" s="1">
+      <c r="B78">
         <v>4374.3999999999996</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="3">
+      <c r="A79" s="2">
         <v>5</v>
       </c>
-      <c r="B79" s="1">
+      <c r="B79">
         <v>4401.7</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="3">
+      <c r="A80" s="2">
         <v>10</v>
       </c>
-      <c r="B80" s="1">
+      <c r="B80">
         <v>4417.6000000000004</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81" s="3">
+      <c r="A81" s="2">
         <v>15</v>
       </c>
-      <c r="B81" s="1">
+      <c r="B81">
         <v>4416.8999999999996</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82" s="3">
+      <c r="A82" s="2">
         <v>20</v>
       </c>
-      <c r="B82" s="1">
+      <c r="B82">
         <v>4332.6000000000004</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83" s="3" t="s">
+      <c r="A83" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B83" s="1">
+      <c r="B83">
         <v>4388.6400000000003</v>
       </c>
     </row>
@@ -21073,7 +20998,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>210</v>
       </c>
       <c r="B2">
@@ -21091,10 +21016,10 @@
       <c r="F2">
         <v>1560</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>211</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>212</v>
       </c>
       <c r="I2">
@@ -21103,7 +21028,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>210</v>
       </c>
       <c r="B3">
@@ -21121,10 +21046,10 @@
       <c r="F3">
         <v>1989</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>213</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" t="s">
         <v>214</v>
       </c>
       <c r="I3">
@@ -21133,7 +21058,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>210</v>
       </c>
       <c r="B4">
@@ -21151,10 +21076,10 @@
       <c r="F4">
         <v>1989</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>215</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" t="s">
         <v>216</v>
       </c>
       <c r="I4">
@@ -21163,7 +21088,7 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>210</v>
       </c>
       <c r="B5">
@@ -21181,10 +21106,10 @@
       <c r="F5">
         <v>1989</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" t="s">
         <v>217</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" t="s">
         <v>218</v>
       </c>
       <c r="I5">
@@ -21193,7 +21118,7 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>210</v>
       </c>
       <c r="B6">
@@ -21211,10 +21136,10 @@
       <c r="F6">
         <v>1716</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" t="s">
         <v>219</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" t="s">
         <v>220</v>
       </c>
       <c r="I6">
@@ -21223,7 +21148,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>210</v>
       </c>
       <c r="B7">
@@ -21241,10 +21166,10 @@
       <c r="F7">
         <v>1794</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" t="s">
         <v>221</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" t="s">
         <v>222</v>
       </c>
       <c r="I7">
@@ -21253,7 +21178,7 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>210</v>
       </c>
       <c r="B8">
@@ -21271,10 +21196,10 @@
       <c r="F8">
         <v>1794</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" t="s">
         <v>223</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" t="s">
         <v>224</v>
       </c>
       <c r="I8">
@@ -21283,7 +21208,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>210</v>
       </c>
       <c r="B9">
@@ -21301,10 +21226,10 @@
       <c r="F9">
         <v>1989</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" t="s">
         <v>225</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" t="s">
         <v>226</v>
       </c>
       <c r="I9">
@@ -21313,7 +21238,7 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>210</v>
       </c>
       <c r="B10">
@@ -21331,10 +21256,10 @@
       <c r="F10">
         <v>1989</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" t="s">
         <v>227</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" t="s">
         <v>228</v>
       </c>
       <c r="I10">
@@ -21343,7 +21268,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>210</v>
       </c>
       <c r="B11">
@@ -21361,10 +21286,10 @@
       <c r="F11">
         <v>1989</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" t="s">
         <v>229</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" t="s">
         <v>230</v>
       </c>
       <c r="I11">
@@ -21373,7 +21298,7 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>210</v>
       </c>
       <c r="B12">
@@ -21391,10 +21316,10 @@
       <c r="F12">
         <v>1989</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" t="s">
         <v>231</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" t="s">
         <v>232</v>
       </c>
       <c r="I12">
@@ -21403,7 +21328,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>210</v>
       </c>
       <c r="B13">
@@ -21421,10 +21346,10 @@
       <c r="F13">
         <v>1716</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" t="s">
         <v>233</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" t="s">
         <v>234</v>
       </c>
       <c r="I13">
@@ -21433,7 +21358,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>210</v>
       </c>
       <c r="B14">
@@ -21451,10 +21376,10 @@
       <c r="F14">
         <v>1638</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" t="s">
         <v>235</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" t="s">
         <v>236</v>
       </c>
       <c r="I14">
@@ -21463,7 +21388,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>210</v>
       </c>
       <c r="B15">
@@ -21481,10 +21406,10 @@
       <c r="F15">
         <v>1716</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" t="s">
         <v>237</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" t="s">
         <v>238</v>
       </c>
       <c r="I15">
@@ -21493,7 +21418,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>210</v>
       </c>
       <c r="B16">
@@ -21511,10 +21436,10 @@
       <c r="F16">
         <v>1989</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" t="s">
         <v>239</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" t="s">
         <v>240</v>
       </c>
       <c r="I16">
@@ -21523,7 +21448,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>210</v>
       </c>
       <c r="B17">
@@ -21541,10 +21466,10 @@
       <c r="F17">
         <v>1989</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" t="s">
         <v>241</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="H17" t="s">
         <v>242</v>
       </c>
       <c r="I17">
@@ -21553,7 +21478,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>210</v>
       </c>
       <c r="B18">
@@ -21571,10 +21496,10 @@
       <c r="F18">
         <v>1989</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" t="s">
         <v>243</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H18" t="s">
         <v>244</v>
       </c>
       <c r="I18">
@@ -21583,7 +21508,7 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>210</v>
       </c>
       <c r="B19">
@@ -21601,10 +21526,10 @@
       <c r="F19">
         <v>1989</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" t="s">
         <v>245</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H19" t="s">
         <v>246</v>
       </c>
       <c r="I19">
@@ -21613,7 +21538,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>210</v>
       </c>
       <c r="B20">
@@ -21631,10 +21556,10 @@
       <c r="F20">
         <v>1989</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" t="s">
         <v>247</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H20" t="s">
         <v>248</v>
       </c>
       <c r="I20">
@@ -21643,7 +21568,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>210</v>
       </c>
       <c r="B21">
@@ -21661,10 +21586,10 @@
       <c r="F21">
         <v>1989</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" t="s">
         <v>249</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" t="s">
         <v>250</v>
       </c>
       <c r="I21">
@@ -21673,7 +21598,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>210</v>
       </c>
       <c r="B22">
@@ -21691,10 +21616,10 @@
       <c r="F22">
         <v>1989</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" t="s">
         <v>251</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" t="s">
         <v>252</v>
       </c>
       <c r="I22">
@@ -21703,7 +21628,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>210</v>
       </c>
       <c r="B23">
@@ -21721,10 +21646,10 @@
       <c r="F23">
         <v>1989</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" t="s">
         <v>251</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" t="s">
         <v>253</v>
       </c>
       <c r="I23">
@@ -21733,7 +21658,7 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>210</v>
       </c>
       <c r="B24">
@@ -21751,10 +21676,10 @@
       <c r="F24">
         <v>1989</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" t="s">
         <v>254</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" t="s">
         <v>255</v>
       </c>
       <c r="I24">
@@ -21763,7 +21688,7 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>210</v>
       </c>
       <c r="B25">
@@ -21781,10 +21706,10 @@
       <c r="F25">
         <v>1989</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" t="s">
         <v>256</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="H25" t="s">
         <v>257</v>
       </c>
       <c r="I25">
@@ -21793,7 +21718,7 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>210</v>
       </c>
       <c r="B26">
@@ -21811,10 +21736,10 @@
       <c r="F26">
         <v>1989</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G26" t="s">
         <v>258</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="H26" t="s">
         <v>259</v>
       </c>
       <c r="I26">
@@ -21823,7 +21748,7 @@
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>210</v>
       </c>
       <c r="B27">
@@ -21841,10 +21766,10 @@
       <c r="F27">
         <v>1989</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G27" t="s">
         <v>260</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="H27" t="s">
         <v>261</v>
       </c>
       <c r="I27">
@@ -21853,7 +21778,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>210</v>
       </c>
       <c r="B28">
@@ -21871,10 +21796,10 @@
       <c r="F28">
         <v>1989</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" t="s">
         <v>262</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" t="s">
         <v>263</v>
       </c>
       <c r="I28">
@@ -21883,7 +21808,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>210</v>
       </c>
       <c r="B29">
@@ -21901,10 +21826,10 @@
       <c r="F29">
         <v>1989</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" t="s">
         <v>264</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="H29" t="s">
         <v>265</v>
       </c>
       <c r="I29">
@@ -21913,7 +21838,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>210</v>
       </c>
       <c r="B30">
@@ -21931,10 +21856,10 @@
       <c r="F30">
         <v>1989</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" t="s">
         <v>266</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="H30" t="s">
         <v>267</v>
       </c>
       <c r="I30">
@@ -21943,7 +21868,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>210</v>
       </c>
       <c r="B31">
@@ -21961,10 +21886,10 @@
       <c r="F31">
         <v>1560</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" t="s">
         <v>268</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="H31" t="s">
         <v>269</v>
       </c>
       <c r="I31">
@@ -21973,7 +21898,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>210</v>
       </c>
       <c r="B32">
@@ -21991,10 +21916,10 @@
       <c r="F32">
         <v>1716</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" t="s">
         <v>270</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="H32" t="s">
         <v>271</v>
       </c>
       <c r="I32">
@@ -22003,7 +21928,7 @@
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>210</v>
       </c>
       <c r="B33">
@@ -22021,10 +21946,10 @@
       <c r="F33">
         <v>1716</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" t="s">
         <v>272</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="H33" t="s">
         <v>273</v>
       </c>
       <c r="I33">
@@ -22033,7 +21958,7 @@
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>210</v>
       </c>
       <c r="B34">
@@ -22051,10 +21976,10 @@
       <c r="F34">
         <v>1989</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G34" t="s">
         <v>274</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="H34" t="s">
         <v>275</v>
       </c>
       <c r="I34">
@@ -22063,7 +21988,7 @@
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>210</v>
       </c>
       <c r="B35">
@@ -22081,10 +22006,10 @@
       <c r="F35">
         <v>1989</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" t="s">
         <v>276</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="H35" t="s">
         <v>277</v>
       </c>
       <c r="I35">
@@ -22093,7 +22018,7 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>210</v>
       </c>
       <c r="B36">
@@ -22111,10 +22036,10 @@
       <c r="F36">
         <v>1989</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G36" t="s">
         <v>278</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="H36" t="s">
         <v>279</v>
       </c>
       <c r="I36">
@@ -22123,7 +22048,7 @@
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>210</v>
       </c>
       <c r="B37">
@@ -22141,10 +22066,10 @@
       <c r="F37">
         <v>1794</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G37" t="s">
         <v>280</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="H37" t="s">
         <v>281</v>
       </c>
       <c r="I37">
@@ -22153,7 +22078,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>210</v>
       </c>
       <c r="B38">
@@ -22171,10 +22096,10 @@
       <c r="F38">
         <v>1716</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="G38" t="s">
         <v>282</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="H38" t="s">
         <v>283</v>
       </c>
       <c r="I38">
@@ -22183,7 +22108,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>210</v>
       </c>
       <c r="B39">
@@ -22201,10 +22126,10 @@
       <c r="F39">
         <v>1638</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" t="s">
         <v>284</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="H39" t="s">
         <v>285</v>
       </c>
       <c r="I39">
@@ -22213,7 +22138,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>210</v>
       </c>
       <c r="B40">
@@ -22231,10 +22156,10 @@
       <c r="F40">
         <v>1989</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G40" t="s">
         <v>286</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H40" t="s">
         <v>287</v>
       </c>
       <c r="I40">
@@ -22243,7 +22168,7 @@
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>210</v>
       </c>
       <c r="B41">
@@ -22261,10 +22186,10 @@
       <c r="F41">
         <v>1989</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G41" t="s">
         <v>288</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H41" t="s">
         <v>289</v>
       </c>
       <c r="I41">
@@ -22273,7 +22198,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>210</v>
       </c>
       <c r="B42">
@@ -22291,10 +22216,10 @@
       <c r="F42">
         <v>1716</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G42" t="s">
         <v>290</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="H42" t="s">
         <v>291</v>
       </c>
       <c r="I42">
@@ -22303,7 +22228,7 @@
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>210</v>
       </c>
       <c r="B43">
@@ -22321,10 +22246,10 @@
       <c r="F43">
         <v>1989</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G43" t="s">
         <v>292</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="H43" t="s">
         <v>293</v>
       </c>
       <c r="I43">
@@ -22333,7 +22258,7 @@
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>210</v>
       </c>
       <c r="B44">
@@ -22351,10 +22276,10 @@
       <c r="F44">
         <v>1638</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="G44" t="s">
         <v>294</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="H44" t="s">
         <v>295</v>
       </c>
       <c r="I44">
@@ -22363,7 +22288,7 @@
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>210</v>
       </c>
       <c r="B45">
@@ -22381,10 +22306,10 @@
       <c r="F45">
         <v>1638</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="G45" t="s">
         <v>296</v>
       </c>
-      <c r="H45" s="1" t="s">
+      <c r="H45" t="s">
         <v>297</v>
       </c>
       <c r="I45">
@@ -22393,7 +22318,7 @@
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>210</v>
       </c>
       <c r="B46">
@@ -22411,10 +22336,10 @@
       <c r="F46">
         <v>1989</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="G46" t="s">
         <v>298</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="H46" t="s">
         <v>299</v>
       </c>
       <c r="I46">
@@ -22423,7 +22348,7 @@
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>210</v>
       </c>
       <c r="B47">
@@ -22441,10 +22366,10 @@
       <c r="F47">
         <v>1638</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="G47" t="s">
         <v>300</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="H47" t="s">
         <v>301</v>
       </c>
       <c r="I47">
@@ -22453,7 +22378,7 @@
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>210</v>
       </c>
       <c r="B48">
@@ -22471,10 +22396,10 @@
       <c r="F48">
         <v>1989</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="G48" t="s">
         <v>302</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="H48" t="s">
         <v>303</v>
       </c>
       <c r="I48">
@@ -22483,7 +22408,7 @@
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>210</v>
       </c>
       <c r="B49">
@@ -22501,10 +22426,10 @@
       <c r="F49">
         <v>1638</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="G49" t="s">
         <v>304</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="H49" t="s">
         <v>305</v>
       </c>
       <c r="I49">
@@ -22513,7 +22438,7 @@
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>210</v>
       </c>
       <c r="B50">
@@ -22531,10 +22456,10 @@
       <c r="F50">
         <v>1989</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="G50" t="s">
         <v>306</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="H50" t="s">
         <v>307</v>
       </c>
       <c r="I50">
@@ -22543,7 +22468,7 @@
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>210</v>
       </c>
       <c r="B51">
@@ -22561,10 +22486,10 @@
       <c r="F51">
         <v>1560</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="G51" t="s">
         <v>308</v>
       </c>
-      <c r="H51" s="1" t="s">
+      <c r="H51" t="s">
         <v>309</v>
       </c>
       <c r="I51">
@@ -22591,7 +22516,7 @@
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="1" t="s">
         <v>105</v>
       </c>
       <c r="B60" t="s">
@@ -22599,95 +22524,95 @@
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="3">
+      <c r="A61" s="2">
         <v>50</v>
       </c>
-      <c r="B61" s="1">
+      <c r="B61">
         <v>1762.8</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="3">
+      <c r="A62" s="2">
         <v>100</v>
       </c>
-      <c r="B62" s="1">
+      <c r="B62">
         <v>1989</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63" s="3">
+      <c r="A63" s="2">
         <v>500</v>
       </c>
-      <c r="B63" s="1">
+      <c r="B63">
         <v>1794</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64" s="3">
+      <c r="A64" s="2">
         <v>1000</v>
       </c>
-      <c r="B64" s="1">
+      <c r="B64">
         <v>1989</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="3">
+      <c r="A65" s="2">
         <v>5000</v>
       </c>
-      <c r="B65" s="1">
+      <c r="B65">
         <v>1825.2</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="3">
+      <c r="A66" s="2">
         <v>10000</v>
       </c>
-      <c r="B66" s="1">
+      <c r="B66">
         <v>1809.6</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="3">
+      <c r="A67" s="2">
         <v>50000</v>
       </c>
-      <c r="B67" s="1">
+      <c r="B67">
         <v>1879.8</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="3">
+      <c r="A68" s="2">
         <v>100000</v>
       </c>
-      <c r="B68" s="1">
+      <c r="B68">
         <v>1911</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="3">
+      <c r="A69" s="2">
         <v>500000</v>
       </c>
-      <c r="B69" s="1">
+      <c r="B69">
         <v>1903.2</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="3">
+      <c r="A70" s="2">
         <v>1000000</v>
       </c>
-      <c r="B70" s="1">
+      <c r="B70">
         <v>1848.6</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="3" t="s">
+      <c r="A71" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B71" s="1">
+      <c r="B71">
         <v>1871.22</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
+      <c r="A77" s="1" t="s">
         <v>105</v>
       </c>
       <c r="B77" t="s">
@@ -22695,50 +22620,50 @@
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="3">
+      <c r="A78" s="2">
         <v>1</v>
       </c>
-      <c r="B78" s="1">
+      <c r="B78">
         <v>1817.4</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="3">
+      <c r="A79" s="2">
         <v>5</v>
       </c>
-      <c r="B79" s="1">
+      <c r="B79">
         <v>1875.9</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="3">
+      <c r="A80" s="2">
         <v>10</v>
       </c>
-      <c r="B80" s="1">
+      <c r="B80">
         <v>1887.6</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81" s="3">
+      <c r="A81" s="2">
         <v>15</v>
       </c>
-      <c r="B81" s="1">
+      <c r="B81">
         <v>1848.6</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82" s="3">
+      <c r="A82" s="2">
         <v>20</v>
       </c>
-      <c r="B82" s="1">
+      <c r="B82">
         <v>1926.6</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83" s="3" t="s">
+      <c r="A83" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B83" s="1">
+      <c r="B83">
         <v>1871.22</v>
       </c>
     </row>
@@ -22796,7 +22721,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>310</v>
       </c>
       <c r="B2">
@@ -22814,10 +22739,10 @@
       <c r="F2">
         <v>4524</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>311</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>312</v>
       </c>
       <c r="I2">
@@ -22826,7 +22751,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>310</v>
       </c>
       <c r="B3">
@@ -22844,19 +22769,19 @@
       <c r="F3">
         <v>4290</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>313</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" t="s">
         <v>314</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I2:I33" si="0">IF(ISNUMBER(G3), G3, SUBSTITUTE(G3, ".", ",")*1)</f>
+        <f t="shared" ref="I3:I33" si="0">IF(ISNUMBER(G3), G3, SUBSTITUTE(G3, ".", ",")*1)</f>
         <v>259.67955613136201</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>310</v>
       </c>
       <c r="B4">
@@ -22874,10 +22799,10 @@
       <c r="F4">
         <v>4602</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>315</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" t="s">
         <v>316</v>
       </c>
       <c r="I4">
@@ -22886,7 +22811,7 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>310</v>
       </c>
       <c r="B5">
@@ -22904,10 +22829,10 @@
       <c r="F5">
         <v>4602</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" t="s">
         <v>317</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" t="s">
         <v>318</v>
       </c>
       <c r="I5">
@@ -22916,7 +22841,7 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>310</v>
       </c>
       <c r="B6">
@@ -22934,10 +22859,10 @@
       <c r="F6">
         <v>4212</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" t="s">
         <v>319</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" t="s">
         <v>320</v>
       </c>
       <c r="I6">
@@ -22946,7 +22871,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>310</v>
       </c>
       <c r="B7">
@@ -22964,10 +22889,10 @@
       <c r="F7">
         <v>4134</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" t="s">
         <v>321</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" t="s">
         <v>322</v>
       </c>
       <c r="I7">
@@ -22976,7 +22901,7 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>310</v>
       </c>
       <c r="B8">
@@ -22994,10 +22919,10 @@
       <c r="F8">
         <v>4953</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" t="s">
         <v>323</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" t="s">
         <v>324</v>
       </c>
       <c r="I8">
@@ -23006,7 +22931,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>310</v>
       </c>
       <c r="B9">
@@ -23024,10 +22949,10 @@
       <c r="F9">
         <v>4524</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" t="s">
         <v>325</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" t="s">
         <v>326</v>
       </c>
       <c r="I9">
@@ -23036,7 +22961,7 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>310</v>
       </c>
       <c r="B10">
@@ -23054,10 +22979,10 @@
       <c r="F10">
         <v>4602</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" t="s">
         <v>327</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" t="s">
         <v>328</v>
       </c>
       <c r="I10">
@@ -23066,7 +22991,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>310</v>
       </c>
       <c r="B11">
@@ -23084,10 +23009,10 @@
       <c r="F11">
         <v>4680</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" t="s">
         <v>329</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" t="s">
         <v>330</v>
       </c>
       <c r="I11">
@@ -23096,7 +23021,7 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>310</v>
       </c>
       <c r="B12">
@@ -23114,10 +23039,10 @@
       <c r="F12">
         <v>4602</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" t="s">
         <v>331</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" t="s">
         <v>332</v>
       </c>
       <c r="I12">
@@ -23126,7 +23051,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>310</v>
       </c>
       <c r="B13">
@@ -23144,10 +23069,10 @@
       <c r="F13">
         <v>4368</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" t="s">
         <v>333</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" t="s">
         <v>334</v>
       </c>
       <c r="I13">
@@ -23156,7 +23081,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>310</v>
       </c>
       <c r="B14">
@@ -23174,10 +23099,10 @@
       <c r="F14">
         <v>4524</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" t="s">
         <v>335</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" t="s">
         <v>336</v>
       </c>
       <c r="I14">
@@ -23186,7 +23111,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>310</v>
       </c>
       <c r="B15">
@@ -23204,10 +23129,10 @@
       <c r="F15">
         <v>4602</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" t="s">
         <v>337</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" t="s">
         <v>338</v>
       </c>
       <c r="I15">
@@ -23216,7 +23141,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>310</v>
       </c>
       <c r="B16">
@@ -23234,10 +23159,10 @@
       <c r="F16">
         <v>4524</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" t="s">
         <v>339</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" t="s">
         <v>340</v>
       </c>
       <c r="I16">
@@ -23246,7 +23171,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>310</v>
       </c>
       <c r="B17">
@@ -23264,10 +23189,10 @@
       <c r="F17">
         <v>5109</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" t="s">
         <v>341</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="H17" t="s">
         <v>342</v>
       </c>
       <c r="I17">
@@ -23276,7 +23201,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>310</v>
       </c>
       <c r="B18">
@@ -23294,10 +23219,10 @@
       <c r="F18">
         <v>4602</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" t="s">
         <v>343</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H18" t="s">
         <v>344</v>
       </c>
       <c r="I18">
@@ -23306,7 +23231,7 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>310</v>
       </c>
       <c r="B19">
@@ -23324,10 +23249,10 @@
       <c r="F19">
         <v>4875</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" t="s">
         <v>345</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H19" t="s">
         <v>346</v>
       </c>
       <c r="I19">
@@ -23336,7 +23261,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>310</v>
       </c>
       <c r="B20">
@@ -23354,10 +23279,10 @@
       <c r="F20">
         <v>5031</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" t="s">
         <v>347</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H20" t="s">
         <v>348</v>
       </c>
       <c r="I20">
@@ -23366,7 +23291,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>310</v>
       </c>
       <c r="B21">
@@ -23384,10 +23309,10 @@
       <c r="F21">
         <v>4680</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" t="s">
         <v>349</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" t="s">
         <v>350</v>
       </c>
       <c r="I21">
@@ -23396,7 +23321,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>310</v>
       </c>
       <c r="B22">
@@ -23414,10 +23339,10 @@
       <c r="F22">
         <v>4875</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" t="s">
         <v>351</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" t="s">
         <v>352</v>
       </c>
       <c r="I22">
@@ -23426,7 +23351,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>310</v>
       </c>
       <c r="B23">
@@ -23444,10 +23369,10 @@
       <c r="F23">
         <v>4602</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" t="s">
         <v>353</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" t="s">
         <v>354</v>
       </c>
       <c r="I23">
@@ -23456,7 +23381,7 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>310</v>
       </c>
       <c r="B24">
@@ -23474,10 +23399,10 @@
       <c r="F24">
         <v>5031</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" t="s">
         <v>355</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" t="s">
         <v>356</v>
       </c>
       <c r="I24">
@@ -23486,7 +23411,7 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>310</v>
       </c>
       <c r="B25">
@@ -23504,10 +23429,10 @@
       <c r="F25">
         <v>5031</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" t="s">
         <v>357</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="H25" t="s">
         <v>358</v>
       </c>
       <c r="I25">
@@ -23516,7 +23441,7 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>310</v>
       </c>
       <c r="B26">
@@ -23534,10 +23459,10 @@
       <c r="F26">
         <v>5109</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G26" t="s">
         <v>359</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="H26" t="s">
         <v>360</v>
       </c>
       <c r="I26">
@@ -23546,7 +23471,7 @@
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>310</v>
       </c>
       <c r="B27">
@@ -23564,10 +23489,10 @@
       <c r="F27">
         <v>4797</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G27" t="s">
         <v>361</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="H27" t="s">
         <v>362</v>
       </c>
       <c r="I27">
@@ -23576,7 +23501,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>310</v>
       </c>
       <c r="B28">
@@ -23594,10 +23519,10 @@
       <c r="F28">
         <v>4602</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" t="s">
         <v>363</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" t="s">
         <v>364</v>
       </c>
       <c r="I28">
@@ -23606,7 +23531,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>310</v>
       </c>
       <c r="B29">
@@ -23624,10 +23549,10 @@
       <c r="F29">
         <v>4134</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" t="s">
         <v>365</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="H29" t="s">
         <v>366</v>
       </c>
       <c r="I29">
@@ -23636,7 +23561,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>310</v>
       </c>
       <c r="B30">
@@ -23654,10 +23579,10 @@
       <c r="F30">
         <v>4602</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" t="s">
         <v>367</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="H30" t="s">
         <v>368</v>
       </c>
       <c r="I30">
@@ -23666,7 +23591,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>310</v>
       </c>
       <c r="B31">
@@ -23684,10 +23609,10 @@
       <c r="F31">
         <v>4602</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" t="s">
         <v>369</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="H31" t="s">
         <v>370</v>
       </c>
       <c r="I31">
@@ -23696,7 +23621,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>310</v>
       </c>
       <c r="B32">
@@ -23714,10 +23639,10 @@
       <c r="F32">
         <v>4290</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" t="s">
         <v>371</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="H32" t="s">
         <v>372</v>
       </c>
       <c r="I32">
@@ -23726,7 +23651,7 @@
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>310</v>
       </c>
       <c r="B33">
@@ -23744,10 +23669,10 @@
       <c r="F33">
         <v>5031</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" t="s">
         <v>373</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="H33" t="s">
         <v>374</v>
       </c>
       <c r="I33">
@@ -23756,7 +23681,7 @@
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>310</v>
       </c>
       <c r="B34">
@@ -23774,10 +23699,10 @@
       <c r="F34">
         <v>4368</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G34" t="s">
         <v>375</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="H34" t="s">
         <v>376</v>
       </c>
       <c r="I34">
@@ -23786,7 +23711,7 @@
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>310</v>
       </c>
       <c r="B35">
@@ -23804,10 +23729,10 @@
       <c r="F35">
         <v>4602</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" t="s">
         <v>377</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="H35" t="s">
         <v>378</v>
       </c>
       <c r="I35">
@@ -23816,7 +23741,7 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>310</v>
       </c>
       <c r="B36">
@@ -23834,10 +23759,10 @@
       <c r="F36">
         <v>4446</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G36" t="s">
         <v>379</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="H36" t="s">
         <v>380</v>
       </c>
       <c r="I36">
@@ -23846,7 +23771,7 @@
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>310</v>
       </c>
       <c r="B37">
@@ -23864,10 +23789,10 @@
       <c r="F37">
         <v>4797</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G37" t="s">
         <v>381</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="H37" t="s">
         <v>382</v>
       </c>
       <c r="I37">
@@ -23876,7 +23801,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>310</v>
       </c>
       <c r="B38">
@@ -23894,10 +23819,10 @@
       <c r="F38">
         <v>4953</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="G38" t="s">
         <v>383</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="H38" t="s">
         <v>384</v>
       </c>
       <c r="I38">
@@ -23906,7 +23831,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>310</v>
       </c>
       <c r="B39">
@@ -23924,10 +23849,10 @@
       <c r="F39">
         <v>4680</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" t="s">
         <v>385</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="H39" t="s">
         <v>386</v>
       </c>
       <c r="I39">
@@ -23936,7 +23861,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>310</v>
       </c>
       <c r="B40">
@@ -23954,10 +23879,10 @@
       <c r="F40">
         <v>4797</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G40" t="s">
         <v>387</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H40" t="s">
         <v>388</v>
       </c>
       <c r="I40">
@@ -23966,7 +23891,7 @@
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>310</v>
       </c>
       <c r="B41">
@@ -23984,10 +23909,10 @@
       <c r="F41">
         <v>4797</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G41" t="s">
         <v>389</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H41" t="s">
         <v>390</v>
       </c>
       <c r="I41">
@@ -23996,7 +23921,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>310</v>
       </c>
       <c r="B42">
@@ -24014,10 +23939,10 @@
       <c r="F42">
         <v>4680</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G42" t="s">
         <v>391</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="H42" t="s">
         <v>392</v>
       </c>
       <c r="I42">
@@ -24026,7 +23951,7 @@
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>310</v>
       </c>
       <c r="B43">
@@ -24044,10 +23969,10 @@
       <c r="F43">
         <v>4875</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G43" t="s">
         <v>393</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="H43" t="s">
         <v>394</v>
       </c>
       <c r="I43">
@@ -24056,7 +23981,7 @@
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>310</v>
       </c>
       <c r="B44">
@@ -24074,10 +23999,10 @@
       <c r="F44">
         <v>4953</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="G44" t="s">
         <v>395</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="H44" t="s">
         <v>396</v>
       </c>
       <c r="I44">
@@ -24086,7 +24011,7 @@
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>310</v>
       </c>
       <c r="B45">
@@ -24104,10 +24029,10 @@
       <c r="F45">
         <v>5031</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="G45" t="s">
         <v>397</v>
       </c>
-      <c r="H45" s="1" t="s">
+      <c r="H45" t="s">
         <v>398</v>
       </c>
       <c r="I45">
@@ -24116,7 +24041,7 @@
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>310</v>
       </c>
       <c r="B46">
@@ -24134,10 +24059,10 @@
       <c r="F46">
         <v>5031</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="G46" t="s">
         <v>399</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="H46" t="s">
         <v>400</v>
       </c>
       <c r="I46">
@@ -24146,7 +24071,7 @@
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>310</v>
       </c>
       <c r="B47">
@@ -24164,10 +24089,10 @@
       <c r="F47">
         <v>4797</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="G47" t="s">
         <v>401</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="H47" t="s">
         <v>402</v>
       </c>
       <c r="I47">
@@ -24176,7 +24101,7 @@
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>310</v>
       </c>
       <c r="B48">
@@ -24194,10 +24119,10 @@
       <c r="F48">
         <v>4953</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="G48" t="s">
         <v>403</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="H48" t="s">
         <v>404</v>
       </c>
       <c r="I48">
@@ -24206,7 +24131,7 @@
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>310</v>
       </c>
       <c r="B49">
@@ -24224,10 +24149,10 @@
       <c r="F49">
         <v>5109</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="G49" t="s">
         <v>405</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="H49" t="s">
         <v>406</v>
       </c>
       <c r="I49">
@@ -24236,7 +24161,7 @@
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>310</v>
       </c>
       <c r="B50">
@@ -24254,10 +24179,10 @@
       <c r="F50">
         <v>4875</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="G50" t="s">
         <v>407</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="H50" t="s">
         <v>408</v>
       </c>
       <c r="I50">
@@ -24266,7 +24191,7 @@
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>310</v>
       </c>
       <c r="B51">
@@ -24284,10 +24209,10 @@
       <c r="F51">
         <v>4875</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="G51" t="s">
         <v>409</v>
       </c>
-      <c r="H51" s="1" t="s">
+      <c r="H51" t="s">
         <v>410</v>
       </c>
       <c r="I51">
@@ -24314,7 +24239,7 @@
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="1" t="s">
         <v>105</v>
       </c>
       <c r="B60" t="s">
@@ -24322,95 +24247,95 @@
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="3">
+      <c r="A61" s="2">
         <v>50</v>
       </c>
-      <c r="B61" s="1">
+      <c r="B61">
         <v>4921.8</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="3">
+      <c r="A62" s="2">
         <v>100</v>
       </c>
-      <c r="B62" s="1">
+      <c r="B62">
         <v>4929.6000000000004</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63" s="3">
+      <c r="A63" s="2">
         <v>500</v>
       </c>
-      <c r="B63" s="1">
+      <c r="B63">
         <v>4914</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64" s="3">
+      <c r="A64" s="2">
         <v>1000</v>
       </c>
-      <c r="B64" s="1">
+      <c r="B64">
         <v>4859.3999999999996</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="3">
+      <c r="A65" s="2">
         <v>5000</v>
       </c>
-      <c r="B65" s="1">
+      <c r="B65">
         <v>4804.8</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="3">
+      <c r="A66" s="2">
         <v>10000</v>
       </c>
-      <c r="B66" s="1">
+      <c r="B66">
         <v>4524</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="3">
+      <c r="A67" s="2">
         <v>50000</v>
       </c>
-      <c r="B67" s="1">
+      <c r="B67">
         <v>4547.3999999999996</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="3">
+      <c r="A68" s="2">
         <v>100000</v>
       </c>
-      <c r="B68" s="1">
+      <c r="B68">
         <v>4578.6000000000004</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="3">
+      <c r="A69" s="2">
         <v>500000</v>
       </c>
-      <c r="B69" s="1">
+      <c r="B69">
         <v>4547.3999999999996</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="3">
+      <c r="A70" s="2">
         <v>1000000</v>
       </c>
-      <c r="B70" s="1">
+      <c r="B70">
         <v>4446</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="3" t="s">
+      <c r="A71" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B71" s="1">
+      <c r="B71">
         <v>4707.3</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
+      <c r="A77" s="1" t="s">
         <v>105</v>
       </c>
       <c r="B77" t="s">
@@ -24418,50 +24343,50 @@
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="3">
+      <c r="A78" s="2">
         <v>1</v>
       </c>
-      <c r="B78" s="1">
+      <c r="B78">
         <v>46605</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="3">
+      <c r="A79" s="2">
         <v>5</v>
       </c>
-      <c r="B79" s="1">
+      <c r="B79">
         <v>46956</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="3">
+      <c r="A80" s="2">
         <v>10</v>
       </c>
-      <c r="B80" s="1">
+      <c r="B80">
         <v>47229</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81" s="3">
+      <c r="A81" s="2">
         <v>15</v>
       </c>
-      <c r="B81" s="1">
+      <c r="B81">
         <v>46800</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82" s="3">
+      <c r="A82" s="2">
         <v>20</v>
       </c>
-      <c r="B82" s="1">
+      <c r="B82">
         <v>47775</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83" s="3" t="s">
+      <c r="A83" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B83" s="1">
+      <c r="B83">
         <v>235365</v>
       </c>
     </row>
@@ -24519,7 +24444,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>411</v>
       </c>
       <c r="B2">
@@ -24537,10 +24462,10 @@
       <c r="F2">
         <v>1002</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>412</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>413</v>
       </c>
       <c r="I2">
@@ -24549,7 +24474,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>411</v>
       </c>
       <c r="B3">
@@ -24567,10 +24492,10 @@
       <c r="F3">
         <v>1002</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>414</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" t="s">
         <v>415</v>
       </c>
       <c r="I3">
@@ -24579,7 +24504,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>411</v>
       </c>
       <c r="B4">
@@ -24597,10 +24522,10 @@
       <c r="F4">
         <v>1005</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>416</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" t="s">
         <v>417</v>
       </c>
       <c r="I4">
@@ -24609,7 +24534,7 @@
       </c>
     </row>
     <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>411</v>
       </c>
       <c r="B5">
@@ -24627,10 +24552,10 @@
       <c r="F5">
         <v>999</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" t="s">
         <v>418</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" t="s">
         <v>419</v>
       </c>
       <c r="I5">
@@ -24639,7 +24564,7 @@
       </c>
     </row>
     <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>411</v>
       </c>
       <c r="B6">
@@ -24657,10 +24582,10 @@
       <c r="F6">
         <v>1002</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" t="s">
         <v>420</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" t="s">
         <v>421</v>
       </c>
       <c r="I6">
@@ -24669,7 +24594,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>411</v>
       </c>
       <c r="B7">
@@ -24687,10 +24612,10 @@
       <c r="F7">
         <v>1002</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" t="s">
         <v>422</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" t="s">
         <v>423</v>
       </c>
       <c r="I7">
@@ -24699,7 +24624,7 @@
       </c>
     </row>
     <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>411</v>
       </c>
       <c r="B8">
@@ -24717,10 +24642,10 @@
       <c r="F8">
         <v>1002</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" t="s">
         <v>424</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" t="s">
         <v>425</v>
       </c>
       <c r="I8">
@@ -24729,7 +24654,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>411</v>
       </c>
       <c r="B9">
@@ -24747,10 +24672,10 @@
       <c r="F9">
         <v>1002</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" t="s">
         <v>426</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" t="s">
         <v>427</v>
       </c>
       <c r="I9">
@@ -24759,7 +24684,7 @@
       </c>
     </row>
     <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>411</v>
       </c>
       <c r="B10">
@@ -24777,10 +24702,10 @@
       <c r="F10">
         <v>1005</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" t="s">
         <v>428</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" t="s">
         <v>429</v>
       </c>
       <c r="I10">
@@ -24789,7 +24714,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>411</v>
       </c>
       <c r="B11">
@@ -24807,10 +24732,10 @@
       <c r="F11">
         <v>999</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" t="s">
         <v>430</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" t="s">
         <v>431</v>
       </c>
       <c r="I11">
@@ -24819,7 +24744,7 @@
       </c>
     </row>
     <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>411</v>
       </c>
       <c r="B12">
@@ -24837,10 +24762,10 @@
       <c r="F12">
         <v>999</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" t="s">
         <v>432</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" t="s">
         <v>433</v>
       </c>
       <c r="I12">
@@ -24849,7 +24774,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>411</v>
       </c>
       <c r="B13">
@@ -24867,10 +24792,10 @@
       <c r="F13">
         <v>1002</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" t="s">
         <v>434</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" t="s">
         <v>435</v>
       </c>
       <c r="I13">
@@ -24879,7 +24804,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>411</v>
       </c>
       <c r="B14">
@@ -24897,10 +24822,10 @@
       <c r="F14">
         <v>1002</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" t="s">
         <v>436</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" t="s">
         <v>437</v>
       </c>
       <c r="I14">
@@ -24909,7 +24834,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>411</v>
       </c>
       <c r="B15">
@@ -24927,10 +24852,10 @@
       <c r="F15">
         <v>1002</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" t="s">
         <v>438</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" t="s">
         <v>439</v>
       </c>
       <c r="I15">
@@ -24939,7 +24864,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>411</v>
       </c>
       <c r="B16">
@@ -24957,10 +24882,10 @@
       <c r="F16">
         <v>1002</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" t="s">
         <v>440</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" t="s">
         <v>441</v>
       </c>
       <c r="I16">
@@ -24969,7 +24894,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>411</v>
       </c>
       <c r="B17">
@@ -24987,10 +24912,10 @@
       <c r="F17">
         <v>1008</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" t="s">
         <v>442</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="H17" t="s">
         <v>443</v>
       </c>
       <c r="I17">
@@ -24999,7 +24924,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>411</v>
       </c>
       <c r="B18">
@@ -25017,10 +24942,10 @@
       <c r="F18">
         <v>1002</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" t="s">
         <v>444</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H18" t="s">
         <v>445</v>
       </c>
       <c r="I18">
@@ -25029,7 +24954,7 @@
       </c>
     </row>
     <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>411</v>
       </c>
       <c r="B19">
@@ -25047,10 +24972,10 @@
       <c r="F19">
         <v>1002</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" t="s">
         <v>446</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H19" t="s">
         <v>447</v>
       </c>
       <c r="I19">
@@ -25059,7 +24984,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>411</v>
       </c>
       <c r="B20">
@@ -25077,10 +25002,10 @@
       <c r="F20">
         <v>1002</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" t="s">
         <v>11</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H20" t="s">
         <v>448</v>
       </c>
       <c r="I20">
@@ -25089,7 +25014,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>411</v>
       </c>
       <c r="B21">
@@ -25107,10 +25032,10 @@
       <c r="F21">
         <v>1002</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" t="s">
         <v>449</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" t="s">
         <v>450</v>
       </c>
       <c r="I21">
@@ -25119,7 +25044,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>411</v>
       </c>
       <c r="B22">
@@ -25137,10 +25062,10 @@
       <c r="F22">
         <v>1002</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" t="s">
         <v>451</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" t="s">
         <v>452</v>
       </c>
       <c r="I22">
@@ -25149,7 +25074,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>411</v>
       </c>
       <c r="B23">
@@ -25167,10 +25092,10 @@
       <c r="F23">
         <v>1002</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" t="s">
         <v>453</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" t="s">
         <v>454</v>
       </c>
       <c r="I23">
@@ -25179,7 +25104,7 @@
       </c>
     </row>
     <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>411</v>
       </c>
       <c r="B24">
@@ -25197,10 +25122,10 @@
       <c r="F24">
         <v>1002</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" t="s">
         <v>455</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" t="s">
         <v>456</v>
       </c>
       <c r="I24">
@@ -25209,7 +25134,7 @@
       </c>
     </row>
     <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>411</v>
       </c>
       <c r="B25">
@@ -25227,10 +25152,10 @@
       <c r="F25">
         <v>1002</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" t="s">
         <v>457</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="H25" t="s">
         <v>458</v>
       </c>
       <c r="I25">
@@ -25239,7 +25164,7 @@
       </c>
     </row>
     <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>411</v>
       </c>
       <c r="B26">
@@ -25257,10 +25182,10 @@
       <c r="F26">
         <v>1005</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G26" t="s">
         <v>459</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="H26" t="s">
         <v>460</v>
       </c>
       <c r="I26">
@@ -25269,7 +25194,7 @@
       </c>
     </row>
     <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>411</v>
       </c>
       <c r="B27">
@@ -25287,10 +25212,10 @@
       <c r="F27">
         <v>1002</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G27" t="s">
         <v>461</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="H27" t="s">
         <v>462</v>
       </c>
       <c r="I27">
@@ -25299,7 +25224,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>411</v>
       </c>
       <c r="B28">
@@ -25317,10 +25242,10 @@
       <c r="F28">
         <v>1005</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" t="s">
         <v>463</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" t="s">
         <v>464</v>
       </c>
       <c r="I28">
@@ -25329,7 +25254,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>411</v>
       </c>
       <c r="B29">
@@ -25347,10 +25272,10 @@
       <c r="F29">
         <v>999</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" t="s">
         <v>465</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="H29" t="s">
         <v>466</v>
       </c>
       <c r="I29">
@@ -25359,7 +25284,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>411</v>
       </c>
       <c r="B30">
@@ -25377,10 +25302,10 @@
       <c r="F30">
         <v>1002</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" t="s">
         <v>467</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="H30" t="s">
         <v>468</v>
       </c>
       <c r="I30">
@@ -25389,7 +25314,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>411</v>
       </c>
       <c r="B31">
@@ -25407,10 +25332,10 @@
       <c r="F31">
         <v>1002</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" t="s">
         <v>469</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="H31" t="s">
         <v>470</v>
       </c>
       <c r="I31">
@@ -25419,7 +25344,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>411</v>
       </c>
       <c r="B32">
@@ -25437,10 +25362,10 @@
       <c r="F32">
         <v>1002</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" t="s">
         <v>471</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="H32" t="s">
         <v>472</v>
       </c>
       <c r="I32">
@@ -25449,7 +25374,7 @@
       </c>
     </row>
     <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>411</v>
       </c>
       <c r="B33">
@@ -25467,10 +25392,10 @@
       <c r="F33">
         <v>1002</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" t="s">
         <v>473</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="H33" t="s">
         <v>474</v>
       </c>
       <c r="I33">
@@ -25479,7 +25404,7 @@
       </c>
     </row>
     <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>411</v>
       </c>
       <c r="B34">
@@ -25497,10 +25422,10 @@
       <c r="F34">
         <v>999</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G34" t="s">
         <v>11</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="H34" t="s">
         <v>475</v>
       </c>
       <c r="I34">
@@ -25509,7 +25434,7 @@
       </c>
     </row>
     <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>411</v>
       </c>
       <c r="B35">
@@ -25527,10 +25452,10 @@
       <c r="F35">
         <v>1002</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" t="s">
         <v>476</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="H35" t="s">
         <v>477</v>
       </c>
       <c r="I35">
@@ -25539,7 +25464,7 @@
       </c>
     </row>
     <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>411</v>
       </c>
       <c r="B36">
@@ -25557,10 +25482,10 @@
       <c r="F36">
         <v>1002</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G36" t="s">
         <v>478</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="H36" t="s">
         <v>479</v>
       </c>
       <c r="I36">
@@ -25569,7 +25494,7 @@
       </c>
     </row>
     <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>411</v>
       </c>
       <c r="B37">
@@ -25587,10 +25512,10 @@
       <c r="F37">
         <v>1002</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G37" t="s">
         <v>480</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="H37" t="s">
         <v>481</v>
       </c>
       <c r="I37">
@@ -25599,7 +25524,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>411</v>
       </c>
       <c r="B38">
@@ -25617,10 +25542,10 @@
       <c r="F38">
         <v>1002</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="G38" t="s">
         <v>482</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="H38" t="s">
         <v>483</v>
       </c>
       <c r="I38">
@@ -25629,7 +25554,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>411</v>
       </c>
       <c r="B39">
@@ -25647,10 +25572,10 @@
       <c r="F39">
         <v>1002</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" t="s">
         <v>484</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="H39" t="s">
         <v>485</v>
       </c>
       <c r="I39">
@@ -25659,7 +25584,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>411</v>
       </c>
       <c r="B40">
@@ -25677,10 +25602,10 @@
       <c r="F40">
         <v>1002</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G40" t="s">
         <v>486</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H40" t="s">
         <v>487</v>
       </c>
       <c r="I40">
@@ -25689,7 +25614,7 @@
       </c>
     </row>
     <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>411</v>
       </c>
       <c r="B41">
@@ -25707,10 +25632,10 @@
       <c r="F41">
         <v>1002</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G41" t="s">
         <v>488</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H41" t="s">
         <v>489</v>
       </c>
       <c r="I41">
@@ -25719,7 +25644,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>411</v>
       </c>
       <c r="B42">
@@ -25737,10 +25662,10 @@
       <c r="F42">
         <v>1002</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G42" t="s">
         <v>490</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="H42" t="s">
         <v>491</v>
       </c>
       <c r="I42">
@@ -25749,7 +25674,7 @@
       </c>
     </row>
     <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>411</v>
       </c>
       <c r="B43">
@@ -25767,10 +25692,10 @@
       <c r="F43">
         <v>1005</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G43" t="s">
         <v>492</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="H43" t="s">
         <v>493</v>
       </c>
       <c r="I43">
@@ -25779,7 +25704,7 @@
       </c>
     </row>
     <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>411</v>
       </c>
       <c r="B44">
@@ -25797,10 +25722,10 @@
       <c r="F44">
         <v>1002</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="G44" t="s">
         <v>438</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="H44" t="s">
         <v>494</v>
       </c>
       <c r="I44">
@@ -25809,7 +25734,7 @@
       </c>
     </row>
     <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>411</v>
       </c>
       <c r="B45">
@@ -25827,10 +25752,10 @@
       <c r="F45">
         <v>1005</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="G45" t="s">
         <v>495</v>
       </c>
-      <c r="H45" s="1" t="s">
+      <c r="H45" t="s">
         <v>496</v>
       </c>
       <c r="I45">
@@ -25839,7 +25764,7 @@
       </c>
     </row>
     <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>411</v>
       </c>
       <c r="B46">
@@ -25857,10 +25782,10 @@
       <c r="F46">
         <v>1005</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="G46" t="s">
         <v>497</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="H46" t="s">
         <v>498</v>
       </c>
       <c r="I46">
@@ -25869,7 +25794,7 @@
       </c>
     </row>
     <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>411</v>
       </c>
       <c r="B47">
@@ -25887,10 +25812,10 @@
       <c r="F47">
         <v>999</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="G47" t="s">
         <v>499</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="H47" t="s">
         <v>500</v>
       </c>
       <c r="I47">
@@ -25899,7 +25824,7 @@
       </c>
     </row>
     <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>411</v>
       </c>
       <c r="B48">
@@ -25917,10 +25842,10 @@
       <c r="F48">
         <v>1002</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="G48" t="s">
         <v>484</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="H48" t="s">
         <v>501</v>
       </c>
       <c r="I48">
@@ -25929,7 +25854,7 @@
       </c>
     </row>
     <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>411</v>
       </c>
       <c r="B49">
@@ -25947,10 +25872,10 @@
       <c r="F49">
         <v>1002</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="G49" t="s">
         <v>484</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="H49" t="s">
         <v>502</v>
       </c>
       <c r="I49">
@@ -25959,7 +25884,7 @@
       </c>
     </row>
     <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>411</v>
       </c>
       <c r="B50">
@@ -25977,10 +25902,10 @@
       <c r="F50">
         <v>1005</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="G50" t="s">
         <v>503</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="H50" t="s">
         <v>504</v>
       </c>
       <c r="I50">
@@ -25989,7 +25914,7 @@
       </c>
     </row>
     <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>411</v>
       </c>
       <c r="B51">
@@ -26007,10 +25932,10 @@
       <c r="F51">
         <v>1002</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="G51" t="s">
         <v>505</v>
       </c>
-      <c r="H51" s="1" t="s">
+      <c r="H51" t="s">
         <v>506</v>
       </c>
       <c r="I51">
@@ -26037,7 +25962,7 @@
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="1" t="s">
         <v>105</v>
       </c>
       <c r="B60" t="s">
@@ -26045,95 +25970,95 @@
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="3">
+      <c r="A61" s="2">
         <v>50</v>
       </c>
-      <c r="B61" s="1">
+      <c r="B61">
         <v>1002</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="3">
+      <c r="A62" s="2">
         <v>100</v>
       </c>
-      <c r="B62" s="1">
+      <c r="B62">
         <v>1002.6</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63" s="3">
+      <c r="A63" s="2">
         <v>500</v>
       </c>
-      <c r="B63" s="1">
+      <c r="B63">
         <v>1003.8</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64" s="3">
+      <c r="A64" s="2">
         <v>1000</v>
       </c>
-      <c r="B64" s="1">
+      <c r="B64">
         <v>1003.2</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="3">
+      <c r="A65" s="2">
         <v>5000</v>
       </c>
-      <c r="B65" s="1">
+      <c r="B65">
         <v>1002</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="3">
+      <c r="A66" s="2">
         <v>10000</v>
       </c>
-      <c r="B66" s="1">
+      <c r="B66">
         <v>1001.4</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="3">
+      <c r="A67" s="2">
         <v>50000</v>
       </c>
-      <c r="B67" s="1">
+      <c r="B67">
         <v>1001.4</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="3">
+      <c r="A68" s="2">
         <v>100000</v>
       </c>
-      <c r="B68" s="1">
+      <c r="B68">
         <v>1002</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="3">
+      <c r="A69" s="2">
         <v>500000</v>
       </c>
-      <c r="B69" s="1">
+      <c r="B69">
         <v>1002</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="3">
+      <c r="A70" s="2">
         <v>1000000</v>
       </c>
-      <c r="B70" s="1">
+      <c r="B70">
         <v>1002</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="3" t="s">
+      <c r="A71" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B71" s="1">
+      <c r="B71">
         <v>1002.24</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
+      <c r="A77" s="1" t="s">
         <v>105</v>
       </c>
       <c r="B77" t="s">
@@ -26141,50 +26066,50 @@
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="3">
+      <c r="A78" s="2">
         <v>1</v>
       </c>
-      <c r="B78" s="1">
+      <c r="B78">
         <v>1002</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="3">
+      <c r="A79" s="2">
         <v>5</v>
       </c>
-      <c r="B79" s="1">
+      <c r="B79">
         <v>1002.3</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="3">
+      <c r="A80" s="2">
         <v>10</v>
       </c>
-      <c r="B80" s="1">
+      <c r="B80">
         <v>1002.6</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81" s="3">
+      <c r="A81" s="2">
         <v>15</v>
       </c>
-      <c r="B81" s="1">
+      <c r="B81">
         <v>1001.7</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82" s="3">
+      <c r="A82" s="2">
         <v>20</v>
       </c>
-      <c r="B82" s="1">
+      <c r="B82">
         <v>1002.6</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83" s="3" t="s">
+      <c r="A83" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B83" s="1">
+      <c r="B83">
         <v>1002.24</v>
       </c>
     </row>

--- a/résultat_Tabou_v2.xlsx
+++ b/résultat_Tabou_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robau\OneDrive\Bureau\Polytech\4A\Optimisation discrète\Projet\knapsack_problem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C5D72F-54C0-40CF-B2DF-95F27ECB35E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13D819B3-1A44-4ABF-BF99-85A180601598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FA556888-71C7-44BA-BCFC-48CD02DC929A}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{FA556888-71C7-44BA-BCFC-48CD02DC929A}"/>
   </bookViews>
   <sheets>
     <sheet name="results_0_fusionné" sheetId="2" r:id="rId1"/>
@@ -34,12 +34,12 @@
   <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId9"/>
-    <pivotCache cacheId="1" r:id="rId10"/>
+    <pivotCache cacheId="22" r:id="rId10"/>
     <pivotCache cacheId="2" r:id="rId11"/>
     <pivotCache cacheId="3" r:id="rId12"/>
     <pivotCache cacheId="4" r:id="rId13"/>
     <pivotCache cacheId="10" r:id="rId14"/>
-    <pivotCache cacheId="16" r:id="rId15"/>
+    <pivotCache cacheId="23" r:id="rId15"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -18209,7 +18209,24 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="4497" maxValue="4556"/>
     </cacheField>
     <cacheField name="Total profit" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="3975" maxValue="4514"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="3975" maxValue="4514" count="16">
+        <n v="4431"/>
+        <n v="4514"/>
+        <n v="4476"/>
+        <n v="4127"/>
+        <n v="4400"/>
+        <n v="4241"/>
+        <n v="4362"/>
+        <n v="4279"/>
+        <n v="3975"/>
+        <n v="4286"/>
+        <n v="4469"/>
+        <n v="4013"/>
+        <n v="4089"/>
+        <n v="4082"/>
+        <n v="4248"/>
+        <n v="4051"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Temps d'execution" numFmtId="0">
       <sharedItems/>
@@ -19087,7 +19104,7 @@
     <x v="0"/>
     <n v="4556"/>
     <n v="4501"/>
-    <n v="4431"/>
+    <x v="0"/>
     <s v="271.08083319664"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_1000000_1_items.csv"/>
     <n v="271.08083319664001"/>
@@ -19098,7 +19115,7 @@
     <x v="1"/>
     <n v="4556"/>
     <n v="4528"/>
-    <n v="4514"/>
+    <x v="1"/>
     <s v="251.1317727565765"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_1000000_10_items.csv"/>
     <n v="251.131772756576"/>
@@ -19109,7 +19126,7 @@
     <x v="2"/>
     <n v="4556"/>
     <n v="4532"/>
-    <n v="4476"/>
+    <x v="2"/>
     <s v="200.94095134735107"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_1000000_15_items.csv"/>
     <n v="200.94095134735099"/>
@@ -19120,7 +19137,7 @@
     <x v="3"/>
     <n v="4556"/>
     <n v="4533"/>
-    <n v="4127"/>
+    <x v="3"/>
     <s v="267.1831636428833"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_1000000_20_items.csv"/>
     <n v="267.18316364288302"/>
@@ -19131,7 +19148,7 @@
     <x v="4"/>
     <n v="4556"/>
     <n v="4540"/>
-    <n v="4400"/>
+    <x v="4"/>
     <s v="332.2588703632355"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_1000000_5_items.csv"/>
     <n v="332.25887036323502"/>
@@ -19142,7 +19159,7 @@
     <x v="0"/>
     <n v="4556"/>
     <n v="4521"/>
-    <n v="4241"/>
+    <x v="5"/>
     <s v="26.69176745414734"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_100000_1_items.csv"/>
     <n v="26.6917674541473"/>
@@ -19153,7 +19170,7 @@
     <x v="1"/>
     <n v="4556"/>
     <n v="4544"/>
-    <n v="4362"/>
+    <x v="6"/>
     <s v="24.015660285949707"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_100000_10_items.csv"/>
     <n v="24.0156602859497"/>
@@ -19164,7 +19181,7 @@
     <x v="2"/>
     <n v="4556"/>
     <n v="4517"/>
-    <n v="4279"/>
+    <x v="7"/>
     <s v="27.432199716567997"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_100000_15_items.csv"/>
     <n v="27.432199716567901"/>
@@ -19175,7 +19192,7 @@
     <x v="3"/>
     <n v="4556"/>
     <n v="4549"/>
-    <n v="3975"/>
+    <x v="8"/>
     <s v="29.74497103691101"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_100000_20_items.csv"/>
     <n v="29.744971036911"/>
@@ -19186,7 +19203,7 @@
     <x v="4"/>
     <n v="4556"/>
     <n v="4532"/>
-    <n v="4476"/>
+    <x v="2"/>
     <s v="24.386036157608032"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_100000_5_items.csv"/>
     <n v="24.386036157608"/>
@@ -19197,7 +19214,7 @@
     <x v="0"/>
     <n v="4556"/>
     <n v="4528"/>
-    <n v="4514"/>
+    <x v="1"/>
     <s v="2.2105422019958496"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_10000_1_items.csv"/>
     <n v="2.2105422019958398"/>
@@ -19208,7 +19225,7 @@
     <x v="1"/>
     <n v="4556"/>
     <n v="4552"/>
-    <n v="4286"/>
+    <x v="9"/>
     <s v="2.273202419281006"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_10000_10_items.csv"/>
     <n v="2.2732024192810001"/>
@@ -19219,7 +19236,7 @@
     <x v="2"/>
     <n v="4556"/>
     <n v="4497"/>
-    <n v="4469"/>
+    <x v="10"/>
     <s v="2.735210418701172"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_10000_15_items.csv"/>
     <n v="2.7352104187011701"/>
@@ -19230,7 +19247,7 @@
     <x v="3"/>
     <n v="4556"/>
     <n v="4545"/>
-    <n v="4013"/>
+    <x v="11"/>
     <s v="2.079288959503174"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_10000_20_items.csv"/>
     <n v="2.0792889595031698"/>
@@ -19241,7 +19258,7 @@
     <x v="4"/>
     <n v="4556"/>
     <n v="4537"/>
-    <n v="4089"/>
+    <x v="12"/>
     <s v="1.95346999168396"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_10000_5_items.csv"/>
     <n v="1.95346999168396"/>
@@ -19252,7 +19269,7 @@
     <x v="0"/>
     <n v="4556"/>
     <n v="4532"/>
-    <n v="4476"/>
+    <x v="2"/>
     <s v="0.2186875343322754"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_1000_1_items.csv"/>
     <n v="0.218687534332275"/>
@@ -19263,7 +19280,7 @@
     <x v="1"/>
     <n v="4556"/>
     <n v="4528"/>
-    <n v="4514"/>
+    <x v="1"/>
     <s v="0.2182381153106689"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_1000_10_items.csv"/>
     <n v="0.218238115310668"/>
@@ -19274,7 +19291,7 @@
     <x v="2"/>
     <n v="4556"/>
     <n v="4528"/>
-    <n v="4514"/>
+    <x v="1"/>
     <s v="0.2766904830932617"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_1000_15_items.csv"/>
     <n v="0.276690483093261"/>
@@ -19285,7 +19302,7 @@
     <x v="3"/>
     <n v="4556"/>
     <n v="4528"/>
-    <n v="4514"/>
+    <x v="1"/>
     <s v="0.2378828525543213"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_1000_20_items.csv"/>
     <n v="0.23788285255432101"/>
@@ -19296,7 +19313,7 @@
     <x v="4"/>
     <n v="4556"/>
     <n v="4528"/>
-    <n v="4514"/>
+    <x v="1"/>
     <s v="0.2913706302642822"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_1000_5_items.csv"/>
     <n v="0.291370630264282"/>
@@ -19307,7 +19324,7 @@
     <x v="0"/>
     <n v="4556"/>
     <n v="4540"/>
-    <n v="4400"/>
+    <x v="4"/>
     <s v="0.0210342407226562"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_100_1_items.csv"/>
     <n v="2.1034240722656201E-2"/>
@@ -19318,7 +19335,7 @@
     <x v="1"/>
     <n v="4556"/>
     <n v="4528"/>
-    <n v="4514"/>
+    <x v="1"/>
     <s v="0.0302066802978515"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_100_10_items.csv"/>
     <n v="3.02066802978515E-2"/>
@@ -19329,7 +19346,7 @@
     <x v="2"/>
     <n v="4556"/>
     <n v="4540"/>
-    <n v="4400"/>
+    <x v="4"/>
     <s v="0.0280330181121826"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_100_15_items.csv"/>
     <n v="2.80330181121826E-2"/>
@@ -19340,7 +19357,7 @@
     <x v="3"/>
     <n v="4556"/>
     <n v="4528"/>
-    <n v="4514"/>
+    <x v="1"/>
     <s v="0.0311417579650878"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_100_20_items.csv"/>
     <n v="3.11417579650878E-2"/>
@@ -19351,7 +19368,7 @@
     <x v="4"/>
     <n v="4556"/>
     <n v="4532"/>
-    <n v="4476"/>
+    <x v="2"/>
     <s v="0.0260205268859863"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_100_5_items.csv"/>
     <n v="2.60205268859863E-2"/>
@@ -19362,7 +19379,7 @@
     <x v="0"/>
     <n v="4556"/>
     <n v="4502"/>
-    <n v="4082"/>
+    <x v="13"/>
     <s v="149.51319432258606"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_500000_1_items.csv"/>
     <n v="149.513194322586"/>
@@ -19373,7 +19390,7 @@
     <x v="1"/>
     <n v="4556"/>
     <n v="4533"/>
-    <n v="4127"/>
+    <x v="3"/>
     <s v="117.74605417251588"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_500000_10_items.csv"/>
     <n v="117.746054172515"/>
@@ -19384,7 +19401,7 @@
     <x v="2"/>
     <n v="4556"/>
     <n v="4532"/>
-    <n v="4476"/>
+    <x v="2"/>
     <s v="127.34297037124634"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_500000_15_items.csv"/>
     <n v="127.342970371246"/>
@@ -19395,7 +19412,7 @@
     <x v="3"/>
     <n v="4556"/>
     <n v="4528"/>
-    <n v="4514"/>
+    <x v="1"/>
     <s v="132.48358607292175"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_500000_20_items.csv"/>
     <n v="132.48358607292101"/>
@@ -19406,7 +19423,7 @@
     <x v="4"/>
     <n v="4556"/>
     <n v="4533"/>
-    <n v="4127"/>
+    <x v="3"/>
     <s v="130.34318709373474"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_500000_5_items.csv"/>
     <n v="130.343187093734"/>
@@ -19417,7 +19434,7 @@
     <x v="0"/>
     <n v="4556"/>
     <n v="4556"/>
-    <n v="4248"/>
+    <x v="14"/>
     <s v="10.025272369384766"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_50000_1_items.csv"/>
     <n v="10.0252723693847"/>
@@ -19428,7 +19445,7 @@
     <x v="1"/>
     <n v="4556"/>
     <n v="4497"/>
-    <n v="4469"/>
+    <x v="10"/>
     <s v="14.63386583328247"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_50000_10_items.csv"/>
     <n v="14.6338658332824"/>
@@ -19439,7 +19456,7 @@
     <x v="2"/>
     <n v="4556"/>
     <n v="4541"/>
-    <n v="4051"/>
+    <x v="15"/>
     <s v="11.29798698425293"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_50000_15_items.csv"/>
     <n v="11.297986984252899"/>
@@ -19450,7 +19467,7 @@
     <x v="3"/>
     <n v="4556"/>
     <n v="4533"/>
-    <n v="4127"/>
+    <x v="3"/>
     <s v="11.255826711654665"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_50000_20_items.csv"/>
     <n v="11.255826711654599"/>
@@ -19461,7 +19478,7 @@
     <x v="4"/>
     <n v="4556"/>
     <n v="4532"/>
-    <n v="4476"/>
+    <x v="2"/>
     <s v="12.47083592414856"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_50000_5_items.csv"/>
     <n v="12.470835924148499"/>
@@ -19472,7 +19489,7 @@
     <x v="0"/>
     <n v="4556"/>
     <n v="4540"/>
-    <n v="4400"/>
+    <x v="4"/>
     <s v="1.0353460311889648"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_5000_1_items.csv"/>
     <n v="1.03534603118896"/>
@@ -19483,7 +19500,7 @@
     <x v="1"/>
     <n v="4556"/>
     <n v="4528"/>
-    <n v="4514"/>
+    <x v="1"/>
     <s v="1.2026267051696775"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_5000_10_items.csv"/>
     <n v="1.20262670516967"/>
@@ -19494,7 +19511,7 @@
     <x v="2"/>
     <n v="4556"/>
     <n v="4528"/>
-    <n v="4514"/>
+    <x v="1"/>
     <s v="1.0795416831970217"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_5000_15_items.csv"/>
     <n v="1.0795416831970199"/>
@@ -19505,7 +19522,7 @@
     <x v="3"/>
     <n v="4556"/>
     <n v="4528"/>
-    <n v="4514"/>
+    <x v="1"/>
     <s v="1.3187153339385986"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_5000_20_items.csv"/>
     <n v="1.31871533393859"/>
@@ -19516,7 +19533,7 @@
     <x v="4"/>
     <n v="4556"/>
     <n v="4497"/>
-    <n v="4469"/>
+    <x v="10"/>
     <s v="1.2598962783813477"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_5000_5_items.csv"/>
     <n v="1.2598962783813401"/>
@@ -19527,7 +19544,7 @@
     <x v="0"/>
     <n v="4556"/>
     <n v="4532"/>
-    <n v="4476"/>
+    <x v="2"/>
     <s v="0.11668062210083"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_500_1_items.csv"/>
     <n v="0.11668062210082999"/>
@@ -19538,7 +19555,7 @@
     <x v="1"/>
     <n v="4556"/>
     <n v="4544"/>
-    <n v="4362"/>
+    <x v="6"/>
     <s v="0.1127166748046875"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_500_10_items.csv"/>
     <n v="0.112716674804687"/>
@@ -19549,7 +19566,7 @@
     <x v="2"/>
     <n v="4556"/>
     <n v="4532"/>
-    <n v="4476"/>
+    <x v="2"/>
     <s v="0.1071124076843261"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_500_15_items.csv"/>
     <n v="0.10711240768432601"/>
@@ -19560,7 +19577,7 @@
     <x v="3"/>
     <n v="4556"/>
     <n v="4528"/>
-    <n v="4514"/>
+    <x v="1"/>
     <s v="0.1321973800659179"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_500_20_items.csv"/>
     <n v="0.132197380065917"/>
@@ -19571,7 +19588,7 @@
     <x v="4"/>
     <n v="4556"/>
     <n v="4528"/>
-    <n v="4514"/>
+    <x v="1"/>
     <s v="0.1184883117675781"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_500_5_items.csv"/>
     <n v="0.118488311767578"/>
@@ -19582,7 +19599,7 @@
     <x v="0"/>
     <n v="4556"/>
     <n v="4532"/>
-    <n v="4476"/>
+    <x v="2"/>
     <s v="0.0100011825561523"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_50_1_items.csv"/>
     <n v="1.00011825561523E-2"/>
@@ -19593,7 +19610,7 @@
     <x v="1"/>
     <n v="4556"/>
     <n v="4528"/>
-    <n v="4514"/>
+    <x v="1"/>
     <s v="0.0145032405853271"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_50_10_items.csv"/>
     <n v="1.45032405853271E-2"/>
@@ -19604,7 +19621,7 @@
     <x v="2"/>
     <n v="4556"/>
     <n v="4528"/>
-    <n v="4514"/>
+    <x v="1"/>
     <s v="0.0119996070861816"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_50_15_items.csv"/>
     <n v="1.1999607086181601E-2"/>
@@ -19615,7 +19632,7 @@
     <x v="3"/>
     <n v="4556"/>
     <n v="4528"/>
-    <n v="4514"/>
+    <x v="1"/>
     <s v="0.0169992446899414"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_50_20_items.csv"/>
     <n v="1.6999244689941399E-2"/>
@@ -19626,7 +19643,7 @@
     <x v="4"/>
     <n v="4556"/>
     <n v="4532"/>
-    <n v="4476"/>
+    <x v="2"/>
     <s v="0.0120341777801513"/>
     <s v="results/1/item_solutions/pi-12-1000-1000-001.kna_50_5_items.csv"/>
     <n v="1.20341777801513E-2"/>
@@ -23033,7 +23050,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{18FEECA9-8FCB-4847-8091-44DAF2F65CD2}" name="Tableau croisé dynamique6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="11">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{18FEECA9-8FCB-4847-8091-44DAF2F65CD2}" name="Tableau croisé dynamique6" cacheId="22" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="11">
   <location ref="A77:B83" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -23108,7 +23125,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0234DE0E-72C6-455B-8329-44A432F67343}" name="Tableau croisé dynamique5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="8">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0234DE0E-72C6-455B-8329-44A432F67343}" name="Tableau croisé dynamique5" cacheId="22" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="8">
   <location ref="A60:B71" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -23203,7 +23220,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C569E52C-1604-435D-A913-10158F911152}" name="Tableau croisé dynamique4" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="8">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C569E52C-1604-435D-A913-10158F911152}" name="Tableau croisé dynamique4" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="8">
   <location ref="A77:B83" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -23278,7 +23295,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7F001CD0-3B75-41F1-BA4D-80B569D61564}" name="Tableau croisé dynamique3" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7F001CD0-3B75-41F1-BA4D-80B569D61564}" name="Tableau croisé dynamique3" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="7">
   <location ref="A60:B71" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -23831,7 +23848,13 @@
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FFBBE3BC-5A03-4FC6-8CE3-D8EFB26519E9}" name="results_4_fusionné" displayName="results_4_fusionné" ref="A1:I51" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:I51" xr:uid="{FFBBE3BC-5A03-4FC6-8CE3-D8EFB26519E9}"/>
+  <autoFilter ref="A1:I51" xr:uid="{FFBBE3BC-5A03-4FC6-8CE3-D8EFB26519E9}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="5109"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{50CBCBEE-1CAB-488B-A51B-C836FBB26818}" uniqueName="1" name="Nom de la base" queryTableFieldId="1" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{6993995D-9C9B-4E10-82D8-39691BD7C872}" uniqueName="2" name="Nombre d'iteration" queryTableFieldId="2"/>
@@ -23851,7 +23874,13 @@
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5C81F8D7-27F5-4E3C-B84A-ABC4F7C1C2CB}" name="results_6_fusionné" displayName="results_6_fusionné" ref="A1:I51" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:I51" xr:uid="{5C81F8D7-27F5-4E3C-B84A-ABC4F7C1C2CB}"/>
+  <autoFilter ref="A1:I51" xr:uid="{5C81F8D7-27F5-4E3C-B84A-ABC4F7C1C2CB}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="1008"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{A216AFCF-A872-4971-93D9-12B970020257}" uniqueName="1" name="Nom de la base" queryTableFieldId="1" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{A69EC5D9-5A2E-4C11-A612-F7AE40718BDA}" uniqueName="2" name="Nombre d'iteration" queryTableFieldId="2"/>
@@ -31148,7 +31177,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>310</v>
       </c>
@@ -31178,7 +31207,7 @@
         <v>213.02613663673401</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>310</v>
       </c>
@@ -31208,7 +31237,7 @@
         <v>259.67955613136201</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>310</v>
       </c>
@@ -31238,7 +31267,7 @@
         <v>260.35935616493202</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>310</v>
       </c>
@@ -31268,7 +31297,7 @@
         <v>268.42133450508101</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>310</v>
       </c>
@@ -31298,7 +31327,7 @@
         <v>239.145867347717</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>310</v>
       </c>
@@ -31328,7 +31357,7 @@
         <v>25.416838884353599</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>310</v>
       </c>
@@ -31358,7 +31387,7 @@
         <v>25.507731199264501</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>310</v>
       </c>
@@ -31388,7 +31417,7 @@
         <v>24.171571731567301</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>310</v>
       </c>
@@ -31418,7 +31447,7 @@
         <v>24.583228111267001</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>310</v>
       </c>
@@ -31448,7 +31477,7 @@
         <v>29.871075630187899</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>310</v>
       </c>
@@ -31478,7 +31507,7 @@
         <v>2.5064721107482901</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>310</v>
       </c>
@@ -31508,7 +31537,7 @@
         <v>2.1455841064453098</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>310</v>
       </c>
@@ -31538,7 +31567,7 @@
         <v>2.5084884166717498</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>310</v>
       </c>
@@ -31568,7 +31597,7 @@
         <v>2.6093401908874498</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>310</v>
       </c>
@@ -31628,7 +31657,7 @@
         <v>0.234714269638061</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>310</v>
       </c>
@@ -31658,7 +31687,7 @@
         <v>0.26364707946777299</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>310</v>
       </c>
@@ -31688,7 +31717,7 @@
         <v>0.230627536773681</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>310</v>
       </c>
@@ -31718,7 +31747,7 @@
         <v>0.25091242790222101</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>310</v>
       </c>
@@ -31748,7 +31777,7 @@
         <v>0.23476743698120101</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>310</v>
       </c>
@@ -31778,7 +31807,7 @@
         <v>2.7999639511108398E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>310</v>
       </c>
@@ -31808,7 +31837,7 @@
         <v>2.3975372314453101E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>310</v>
       </c>
@@ -31838,7 +31867,7 @@
         <v>2.9999971389770501E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>310</v>
       </c>
@@ -31898,7 +31927,7 @@
         <v>2.90296077728271E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>310</v>
       </c>
@@ -31928,7 +31957,7 @@
         <v>99.015268087387</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>310</v>
       </c>
@@ -31958,7 +31987,7 @@
         <v>143.12851238250701</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>310</v>
       </c>
@@ -31988,7 +32017,7 @@
         <v>151.146419525146</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>310</v>
       </c>
@@ -32018,7 +32047,7 @@
         <v>125.42586922645501</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>310</v>
       </c>
@@ -32048,7 +32077,7 @@
         <v>133.349657297134</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>310</v>
       </c>
@@ -32078,7 +32107,7 @@
         <v>11.113141298294</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>310</v>
       </c>
@@ -32108,7 +32137,7 @@
         <v>11.993535518646199</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>310</v>
       </c>
@@ -32138,7 +32167,7 @@
         <v>15.071959257125799</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>310</v>
       </c>
@@ -32168,7 +32197,7 @@
         <v>13.1356954574584</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>310</v>
       </c>
@@ -32198,7 +32227,7 @@
         <v>11.1153483390808</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>310</v>
       </c>
@@ -32228,7 +32257,7 @@
         <v>1.21193099021911</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>310</v>
       </c>
@@ -32258,7 +32287,7 @@
         <v>1.4484531879425</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>310</v>
       </c>
@@ -32288,7 +32317,7 @@
         <v>1.2206552028655999</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>310</v>
       </c>
@@ -32318,7 +32347,7 @@
         <v>1.2179751396179199</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>310</v>
       </c>
@@ -32348,7 +32377,7 @@
         <v>1.3949222564697199</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>310</v>
       </c>
@@ -32378,7 +32407,7 @@
         <v>0.10751390457153299</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>310</v>
       </c>
@@ -32408,7 +32437,7 @@
         <v>0.121551513671875</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>310</v>
       </c>
@@ -32438,7 +32467,7 @@
         <v>0.13614010810852001</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>310</v>
       </c>
@@ -32468,7 +32497,7 @@
         <v>0.12754201889038</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>310</v>
       </c>
@@ -32498,7 +32527,7 @@
         <v>0.121034383773803</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>310</v>
       </c>
@@ -32528,7 +32557,7 @@
         <v>1.1998176574707E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>310</v>
       </c>
@@ -32588,7 +32617,7 @@
         <v>1.70750617980957E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>310</v>
       </c>
@@ -32618,7 +32647,7 @@
         <v>1.39977931976318E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>310</v>
       </c>
@@ -32871,7 +32900,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>411</v>
       </c>
@@ -32901,7 +32930,7 @@
         <v>19.119575262069699</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>411</v>
       </c>
@@ -32931,7 +32960,7 @@
         <v>9.6917152404779995E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>411</v>
       </c>
@@ -32961,7 +32990,7 @@
         <v>1.9989013671875E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>411</v>
       </c>
@@ -32991,7 +33020,7 @@
         <v>1.0018348693846999E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>411</v>
       </c>
@@ -33021,7 +33050,7 @@
         <v>23.432671546936</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>411</v>
       </c>
@@ -33051,7 +33080,7 @@
         <v>1.9012548923492401</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>411</v>
       </c>
@@ -33081,7 +33110,7 @@
         <v>1.0004043579101001E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>411</v>
       </c>
@@ -33111,7 +33140,7 @@
         <v>2.5131247043609601</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>411</v>
       </c>
@@ -33141,7 +33170,7 @@
         <v>2.3696627616882302</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>411</v>
       </c>
@@ -33171,7 +33200,7 @@
         <v>2.1761944293975799</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>411</v>
       </c>
@@ -33201,7 +33230,7 @@
         <v>0.20918869972229001</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>411</v>
       </c>
@@ -33231,7 +33260,7 @@
         <v>0.23622465133666901</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>411</v>
       </c>
@@ -33261,7 +33290,7 @@
         <v>9.6797943115229995E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>411</v>
       </c>
@@ -33291,7 +33320,7 @@
         <v>9.9635124206539998E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>411</v>
       </c>
@@ -33351,7 +33380,7 @@
         <v>2.3031949996948201E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>411</v>
       </c>
@@ -33381,7 +33410,7 @@
         <v>2.3999214172363201E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>411</v>
       </c>
@@ -33411,7 +33440,7 @@
         <v>1.0032653808593E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>411</v>
       </c>
@@ -33441,7 +33470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>411</v>
       </c>
@@ -33471,7 +33500,7 @@
         <v>2.3160934448242101E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>411</v>
       </c>
@@ -33501,7 +33530,7 @@
         <v>3.0345916748045999E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>411</v>
       </c>
@@ -33531,7 +33560,7 @@
         <v>1.9981861114500999E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>411</v>
       </c>
@@ -33561,7 +33590,7 @@
         <v>4.0004253387450998E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>411</v>
       </c>
@@ -33591,7 +33620,7 @@
         <v>1.0011196136474E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>411</v>
       </c>
@@ -33621,7 +33650,7 @@
         <v>3.0016899108885999E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>411</v>
       </c>
@@ -33651,7 +33680,7 @@
         <v>12.264229536056501</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>411</v>
       </c>
@@ -33681,7 +33710,7 @@
         <v>12.321033954620299</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>411</v>
       </c>
@@ -33711,7 +33740,7 @@
         <v>9.7298622131340002E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>411</v>
       </c>
@@ -33741,7 +33770,7 @@
         <v>2.0327568054199002E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>411</v>
       </c>
@@ -33771,7 +33800,7 @@
         <v>12.3816685676574</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>411</v>
       </c>
@@ -33801,7 +33830,7 @@
         <v>0.99103164672851496</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>411</v>
       </c>
@@ -33831,7 +33860,7 @@
         <v>1.32693886756896</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>411</v>
       </c>
@@ -33861,7 +33890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>411</v>
       </c>
@@ -33891,7 +33920,7 @@
         <v>1.0085105895996001E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>411</v>
       </c>
@@ -33921,7 +33950,7 @@
         <v>1.40893650054931</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>411</v>
       </c>
@@ -33951,7 +33980,7 @@
         <v>0.10659146308898899</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>411</v>
       </c>
@@ -33981,7 +34010,7 @@
         <v>9.5915794372549996E-4</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>411</v>
       </c>
@@ -34011,7 +34040,7 @@
         <v>9.9968910217279995E-4</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>411</v>
       </c>
@@ -34041,7 +34070,7 @@
         <v>9.6464157104489997E-4</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>411</v>
       </c>
@@ -34071,7 +34100,7 @@
         <v>0.110260248184204</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>411</v>
       </c>
@@ -34101,7 +34130,7 @@
         <v>1.0104894638061499E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>411</v>
       </c>
@@ -34131,7 +34160,7 @@
         <v>1.21428966522216E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>411</v>
       </c>
@@ -34161,7 +34190,7 @@
         <v>9.9635124206539998E-4</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>411</v>
       </c>
@@ -34191,7 +34220,7 @@
         <v>1.0371208190916999E-3</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>411</v>
       </c>
@@ -34221,7 +34250,7 @@
         <v>1.10344886779785E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>411</v>
       </c>
@@ -34251,7 +34280,7 @@
         <v>2.0036697387695E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>411</v>
       </c>
@@ -34281,7 +34310,7 @@
         <v>9.9968910217279995E-4</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>411</v>
       </c>
@@ -34311,7 +34340,7 @@
         <v>9.9968910217279995E-4</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>411</v>
       </c>
@@ -34341,7 +34370,7 @@
         <v>1.9998550415039002E-3</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>411</v>
       </c>
